--- a/Workpiece for tool.xlsx
+++ b/Workpiece for tool.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atsus\bin\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398B6CF1-D7CC-441E-B289-0E98127D4B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87664B9C-A23F-4362-9567-84C79F81E9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="1335" windowWidth="23490" windowHeight="15015" activeTab="3" xr2:uid="{B1CDC31F-9E0C-410F-B3F2-978CA58E71C8}"/>
+    <workbookView xWindow="2760" yWindow="1335" windowWidth="25350" windowHeight="15015" xr2:uid="{B1CDC31F-9E0C-410F-B3F2-978CA58E71C8}"/>
   </bookViews>
   <sheets>
     <sheet name="public" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="67">
   <si>
     <t>Use at your own risk.</t>
     <phoneticPr fontId="1"/>
@@ -1515,24 +1515,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　　 　　　　　　　　PowerShell</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　　　　　　　　　　 PowerShell</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>GIMP等にてHight:24pxにリサイズの事!!!</t>
-    <rPh sb="4" eb="5">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>コト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="6"/>
@@ -1708,27 +1690,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>perl tools repository</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>python tools repository</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>shell tools repository</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>VisualBASIC tools repository</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>VBscript tools repository</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>powershell tools repository</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1860,12 +1826,166 @@
     <t>JonesyScreenSaver.py</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>BASH tools repository</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Python tools repository</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Perl tools repository</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="22"/>
+        <color rgb="FF66FFFF"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>PowerShell</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="22"/>
+        <color rgb="FF66FFFF"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> tools repository</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="20"/>
+        <color rgb="FF66FFFF"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Visual BASIC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="20"/>
+        <color rgb="FF66FFFF"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>tools</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="20"/>
+        <color rgb="FF66FFFF"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="20"/>
+        <color rgb="FF66FFFF"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>repository</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="22"/>
+        <color rgb="FF0066FF"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>PowerShell</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="22"/>
+        <color rgb="FF0066FF"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> tools repository</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>　・変換対象文字列には</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>正規表現</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>が使用できます。</t>
+    </r>
+    <rPh sb="2" eb="4">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>セイキヒョウゲン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="60" x14ac:knownFonts="1">
+  <fonts count="66" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2180,22 +2300,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF66FFFF"/>
-      <name val="Yu Gothic UI Semibold"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF0066FF"/>
-      <name val="Yu Gothic UI Semibold"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="22"/>
       <color rgb="FFCC00FF"/>
@@ -2327,6 +2431,73 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="22"/>
+      <color rgb="FF66FFFF"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="22"/>
+      <color rgb="FF66FFFF"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="20"/>
+      <color rgb="FF66FFFF"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="20"/>
+      <color rgb="FF66FFFF"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="18"/>
+      <color rgb="FF0066FF"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="22"/>
+      <color rgb="FF0066FF"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="22"/>
+      <color rgb="FF0066FF"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FFFFC000"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2366,81 +2537,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="17">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color theme="0"/>
-      </top>
-      <bottom style="hair">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="0"/>
-      </left>
-      <right style="hair">
-        <color theme="0"/>
-      </right>
-      <top style="hair">
-        <color theme="0"/>
-      </top>
-      <bottom style="hair">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="0"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2615,7 +2717,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2744,21 +2846,6 @@
     <xf numFmtId="0" fontId="38" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -2768,11 +2855,35 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2780,34 +2891,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="40" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1">
@@ -2819,67 +2921,52 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="40" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2888,37 +2975,49 @@
     <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="52" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="57" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="59" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2931,6 +3030,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFC000"/>
+      <color rgb="FFFF9933"/>
       <color rgb="FF0066FF"/>
       <color rgb="FFCCFFFF"/>
       <color rgb="FF0D1117"/>
@@ -2939,8 +3040,6 @@
       <color rgb="FFFFFFFF"/>
       <color rgb="FFFF9900"/>
       <color rgb="FF00FFFF"/>
-      <color rgb="FF201F1E"/>
-      <color rgb="FFFF0066"/>
     </mruColors>
   </colors>
   <extLst>
@@ -4728,138 +4827,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>499110</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="図 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7AFC20A-B261-823E-DB38-87DC19E2DDBB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="754380" y="1592580"/>
-          <a:ext cx="361950" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>128589</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>493641</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="図 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEBFFAF0-2762-690E-6ACD-7621290FD7CF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="716280" y="3382329"/>
-          <a:ext cx="361950" cy="365052"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>133351</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>94298</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>479749</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>458317</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="図 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A7E7E45-59D1-23C1-0839-76206741AA63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="716281" y="4452938"/>
-          <a:ext cx="346398" cy="364019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>305162</xdr:colOff>
       <xdr:row>8</xdr:row>
@@ -5050,485 +5017,6 @@
         <a:xfrm>
           <a:off x="7832217" y="7408376"/>
           <a:ext cx="258903" cy="259566"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>499110</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="図 70">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{844105E7-FF4E-E29E-E730-65A09795C560}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6134100" y="1584960"/>
-          <a:ext cx="361950" cy="361950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>128589</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>493641</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="図 71">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CE06712-8DFA-F94C-45F2-E6D4A5FC2A5E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6134100" y="3262314"/>
-          <a:ext cx="361950" cy="365052"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>94298</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>470223</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>458317</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="図 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAD59634-0CBE-6F50-2AA3-86E9E6F56842}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6134100" y="4418648"/>
-          <a:ext cx="346398" cy="364019"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>557937</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>27191</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="398154" cy="158852"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B8E4A7-C1D8-42EE-A7A7-11845B26D5A6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1138962" y="8904491"/>
-          <a:ext cx="398154" cy="158852"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>426127</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>29983</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="191511" cy="143852"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC1257B3-F3E1-44EE-A069-FAF181B57565}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1578652" y="8907283"/>
-          <a:ext cx="191511" cy="143852"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>400900</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>30960</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>435768</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>173835</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="直線コネクタ 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97C7AC0-5A15-4A4B-A033-C0C1EDE3965C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1553425" y="8908260"/>
-          <a:ext cx="34868" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFC000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>557937</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>24810</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="398154" cy="158852"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AF28C21-7345-BE46-4D89-409514CEF949}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1138962" y="9102135"/>
-          <a:ext cx="398154" cy="158852"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>426127</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>27602</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="191511" cy="143852"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CAF68D7-D054-6296-0FC6-8EA7808B0DE8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1578652" y="9104927"/>
-          <a:ext cx="191511" cy="143852"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>400900</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>28579</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>435768</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>171454</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="直線コネクタ 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E07DEEC0-5399-2893-EC08-1863489286B6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1553425" y="9105904"/>
-          <a:ext cx="34868" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="50000"/>
-              <a:lumOff val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="398154" cy="158852"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78167042-C50E-4AE3-862D-008F0B180BEF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6581775" y="8277225"/>
-          <a:ext cx="398154" cy="158852"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="398154" cy="158852"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EDC0191-F9B6-4EC3-A7A9-2E2AF7A5CE7F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1152525" y="8277225"/>
-          <a:ext cx="398154" cy="158852"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5743,6 +5231,270 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>133351</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>148525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>494963</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>513380</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB40C47F-0E05-0C82-18EE-A6B6F37CF48C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="714537" y="2160076"/>
+          <a:ext cx="361612" cy="364855"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>108611</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>148525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>470223</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>513380</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FBC039B-24FB-052D-C840-05B2775A5D4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6233670" y="2160076"/>
+          <a:ext cx="361612" cy="364855"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>105380</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>93637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>466991</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>458492</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E754D58B-4537-446F-491E-CB0047951A8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6230439" y="5159645"/>
+          <a:ext cx="361611" cy="364855"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>110748</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>93637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>472359</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>458492</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="図 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4533C36F-F10E-5DB8-5593-AC72634C6FA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="691934" y="5159645"/>
+          <a:ext cx="361611" cy="364855"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>110748</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>93636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>456836</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>455263</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDB784C9-34A5-7301-AFD9-C9DBF958C247}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="691934" y="3684077"/>
+          <a:ext cx="346088" cy="361627"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>105380</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>93636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>451468</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>455263</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF68F51B-28A7-4BC1-CCB8-55461D0C7F32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6230439" y="3684077"/>
+          <a:ext cx="346088" cy="361627"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7671,138 +7423,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>187325</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>202335</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>17319</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>12989</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="正方形/長方形 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E839C5C7-03BF-4B6C-B6D5-09F247B5F5B1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6889461" y="5925994"/>
-          <a:ext cx="5172653" cy="728518"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="25400">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>190499</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>203489</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>17318</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="正方形/長方形 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95C1278A-FD11-49BF-839A-D80CADE003CC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="389658" y="5927148"/>
-          <a:ext cx="5169478" cy="733426"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="25400">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -8023,72 +7643,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>187325</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>202335</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>17319</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>12989</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="正方形/長方形 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15DBE053-2888-4294-8E2C-00A6A5D26EBA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6889461" y="6843858"/>
-          <a:ext cx="5172653" cy="728517"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="25400">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -8587,21 +8141,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>190499</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>201930</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>203489</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>17318</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="正方形/長方形 51">
+        <xdr:cNvPr id="43" name="正方形/長方形 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7772E77C-7131-37AC-3834-94EE789BDD58}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F238F2CB-9F32-9DC7-2D43-075B72B6FF3B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8609,8 +8163,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="392429" y="6854190"/>
-          <a:ext cx="5172249" cy="725804"/>
+          <a:off x="392429" y="5937539"/>
+          <a:ext cx="4408806" cy="733772"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8619,6 +8173,204 @@
         <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>203489</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="正方形/長方形 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3ED9D7C-E11E-CBFD-0093-1352E30D76D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="392429" y="6855749"/>
+          <a:ext cx="4408806" cy="733772"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>187326</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>203489</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="正方形/長方形 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3986AAD6-C9A7-F9C6-2B67-2145B5E1B17A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6900546" y="5937539"/>
+          <a:ext cx="4411979" cy="730596"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>187326</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>207299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>19685</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="正方形/長方形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2F5956-DECC-D56C-D455-FC7142F225E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6900546" y="6859559"/>
+          <a:ext cx="4411979" cy="730596"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
@@ -10971,7 +10723,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B6A63E-25D5-4BD7-93A4-A70981612B63}">
-  <dimension ref="B2:S76"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B2:S77"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
@@ -10994,8 +10747,8 @@
       <c r="B3" s="33"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C4" s="53" t="s">
-        <v>42</v>
+      <c r="C4" s="48" t="s">
+        <v>39</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -11005,7 +10758,7 @@
       <c r="I4" s="4"/>
       <c r="K4" s="27"/>
       <c r="L4" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M4" s="27"/>
       <c r="N4" s="27"/>
@@ -11015,7 +10768,7 @@
       <c r="R4" s="27"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C5" s="53"/>
+      <c r="C5" s="48"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -11056,9 +10809,9 @@
     </row>
     <row r="7" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="4"/>
-      <c r="D7" s="80"/>
+      <c r="D7" s="75"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="81" t="s">
+      <c r="F7" s="76" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="4"/>
@@ -11068,7 +10821,7 @@
       <c r="L7" s="10"/>
       <c r="M7" s="22"/>
       <c r="N7" s="10"/>
-      <c r="O7" s="83" t="s">
+      <c r="O7" s="78" t="s">
         <v>0</v>
       </c>
       <c r="P7" s="10"/>
@@ -11304,7 +11057,7 @@
     </row>
     <row r="19" spans="3:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C19" s="8" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -11428,7 +11181,7 @@
     </row>
     <row r="25" spans="3:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C25" s="8" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -11508,7 +11261,7 @@
     </row>
     <row r="29" spans="3:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C29" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -11519,7 +11272,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="27"/>
       <c r="L29" s="28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M29" s="28"/>
       <c r="N29" s="28"/>
@@ -11683,12 +11436,10 @@
       <c r="S37" s="2"/>
     </row>
     <row r="38" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C38" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
@@ -11703,14 +11454,14 @@
       <c r="S38" s="2"/>
     </row>
     <row r="39" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="K39" s="27"/>
+      <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
@@ -11720,21 +11471,17 @@
       <c r="R39" s="10"/>
     </row>
     <row r="40" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C40" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="D40" s="48"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="4"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="M40" s="51"/>
-      <c r="N40" s="52"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
       <c r="O40" s="10"/>
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
@@ -11748,7 +11495,7 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="K41" s="27"/>
+      <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -11765,6 +11512,14 @@
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
     </row>
     <row r="43" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C43" s="4"/>
@@ -11774,6 +11529,14 @@
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
     </row>
     <row r="44" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C44" s="4"/>
@@ -11783,6 +11546,14 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
     </row>
     <row r="45" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C45" s="4"/>
@@ -11792,6 +11563,14 @@
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
     </row>
     <row r="46" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C46" s="4"/>
@@ -11801,6 +11580,14 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
     </row>
     <row r="47" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C47" s="4"/>
@@ -11810,6 +11597,14 @@
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C48" s="4"/>
@@ -11819,8 +11614,16 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -11828,8 +11631,16 @@
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-    </row>
-    <row r="50" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -11837,8 +11648,16 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -11846,8 +11665,16 @@
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-    </row>
-    <row r="52" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -11855,8 +11682,16 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -11864,8 +11699,16 @@
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-    </row>
-    <row r="54" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -11873,8 +11716,16 @@
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-    </row>
-    <row r="55" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -11882,8 +11733,16 @@
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-    </row>
-    <row r="56" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -11891,8 +11750,16 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -11900,8 +11767,16 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-    </row>
-    <row r="58" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K57" s="10"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -11909,8 +11784,16 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K58" s="10"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -11918,8 +11801,16 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-    </row>
-    <row r="60" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K59" s="10"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -11927,8 +11818,16 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-    </row>
-    <row r="61" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K60" s="10"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -11936,8 +11835,16 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -11945,8 +11852,16 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-    </row>
-    <row r="63" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -11954,8 +11869,16 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-    </row>
-    <row r="64" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K63" s="10"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -11963,8 +11886,16 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-    </row>
-    <row r="65" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
+    </row>
+    <row r="65" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -11972,8 +11903,16 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-    </row>
-    <row r="66" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+    </row>
+    <row r="66" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -11981,8 +11920,16 @@
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-    </row>
-    <row r="67" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K66" s="10"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
+    </row>
+    <row r="67" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -11990,8 +11937,16 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
+    </row>
+    <row r="68" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -11999,8 +11954,16 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-    </row>
-    <row r="69" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K68" s="10"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
+    </row>
+    <row r="69" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -12008,8 +11971,16 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-    </row>
-    <row r="70" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K69" s="10"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+    </row>
+    <row r="70" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -12017,8 +11988,16 @@
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-    </row>
-    <row r="71" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K70" s="10"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
+    </row>
+    <row r="71" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -12026,8 +12005,16 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-    </row>
-    <row r="72" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+    </row>
+    <row r="72" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -12035,8 +12022,16 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-    </row>
-    <row r="73" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K72" s="10"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
+    </row>
+    <row r="73" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -12044,8 +12039,16 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-    </row>
-    <row r="74" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K73" s="10"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+    </row>
+    <row r="74" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -12053,8 +12056,16 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
+    </row>
+    <row r="75" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -12062,8 +12073,16 @@
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="K75" s="10"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+    </row>
+    <row r="76" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -12071,6 +12090,24 @@
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="10"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
+    </row>
+    <row r="77" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="K77" s="10"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="10"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -12081,6 +12118,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{602761BE-789F-4222-9DD8-89B2285BFD88}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="B2:U159"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12095,21 +12133,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="90" t="str" cm="1">
+      <c r="B2" s="85" t="str" cm="1">
         <f t="array" aca="1" ref="B2" ca="1">RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1)))</f>
         <v>repos</v>
       </c>
     </row>
     <row r="3" spans="2:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="90"/>
-      <c r="C3" s="53" t="s">
-        <v>54</v>
+      <c r="B3" s="85"/>
+      <c r="C3" s="48" t="s">
+        <v>47</v>
       </c>
-      <c r="K3" s="54"/>
+      <c r="K3" s="49"/>
       <c r="L3" s="27"/>
       <c r="M3" s="27"/>
       <c r="N3" s="10" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O3" s="27"/>
       <c r="P3" s="27"/>
@@ -12122,7 +12160,7 @@
     <row r="4" spans="2:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="13"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="55"/>
+      <c r="K4" s="50"/>
       <c r="L4" s="28"/>
       <c r="M4" s="28"/>
       <c r="N4" s="28"/>
@@ -12135,82 +12173,82 @@
       <c r="U4" s="27"/>
     </row>
     <row r="5" spans="2:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="56"/>
-      <c r="D5" s="57" t="s">
+      <c r="C5" s="51"/>
+      <c r="D5" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="59"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="54"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="55"/>
+      <c r="K5" s="50"/>
       <c r="L5" s="28"/>
       <c r="M5" s="28"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="78" t="s">
+      <c r="N5" s="65"/>
+      <c r="O5" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="72"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="67"/>
       <c r="T5" s="27"/>
       <c r="U5" s="27"/>
     </row>
     <row r="6" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="60"/>
-      <c r="D6" s="61"/>
-      <c r="F6" s="81" t="s">
+      <c r="C6" s="55"/>
+      <c r="D6" s="56"/>
+      <c r="F6" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="62"/>
-      <c r="H6" s="63"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="58"/>
       <c r="J6" s="8"/>
-      <c r="K6" s="55"/>
+      <c r="K6" s="50"/>
       <c r="L6" s="28"/>
       <c r="M6" s="28"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="63"/>
       <c r="P6" s="27"/>
-      <c r="Q6" s="82" t="s">
+      <c r="Q6" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="74"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="69"/>
       <c r="T6" s="27"/>
       <c r="U6" s="27"/>
     </row>
     <row r="7" spans="2:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="64"/>
-      <c r="D7" s="65" t="s">
-        <v>39</v>
+      <c r="C7" s="59"/>
+      <c r="D7" s="60" t="s">
+        <v>36</v>
       </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="67"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="50"/>
       <c r="L7" s="28"/>
       <c r="M7" s="28"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="79" t="s">
-        <v>41</v>
+      <c r="N7" s="70"/>
+      <c r="O7" s="74" t="s">
+        <v>38</v>
       </c>
-      <c r="P7" s="76"/>
-      <c r="Q7" s="76"/>
-      <c r="R7" s="76"/>
-      <c r="S7" s="77"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="72"/>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
     </row>
     <row r="8" spans="2:21" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="D8" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="55"/>
+      <c r="K8" s="50"/>
       <c r="L8" s="28"/>
       <c r="M8" s="28"/>
       <c r="N8" s="28"/>
@@ -12223,7 +12261,7 @@
       <c r="U8" s="27"/>
     </row>
     <row r="9" spans="2:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K9" s="54"/>
+      <c r="K9" s="49"/>
       <c r="L9" s="27"/>
       <c r="M9" s="27"/>
       <c r="N9" s="27"/>
@@ -12236,55 +12274,55 @@
       <c r="U9" s="27"/>
     </row>
     <row r="10" spans="2:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="56"/>
-      <c r="D10" s="57" t="s">
+      <c r="C10" s="51"/>
+      <c r="D10" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="59"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="54"/>
       <c r="J10" s="8"/>
-      <c r="K10" s="55"/>
+      <c r="K10" s="50"/>
       <c r="L10" s="28"/>
       <c r="M10" s="28"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="78" t="s">
+      <c r="N10" s="65"/>
+      <c r="O10" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="72"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="67"/>
       <c r="T10" s="27"/>
       <c r="U10" s="27"/>
     </row>
     <row r="11" spans="2:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="64"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="85" t="s">
+      <c r="C11" s="59"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="G11" s="86"/>
-      <c r="H11" s="67"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="62"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="55"/>
+      <c r="K11" s="50"/>
       <c r="L11" s="28"/>
       <c r="M11" s="28"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="87"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="88" t="s">
+      <c r="N11" s="70"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="R11" s="89"/>
-      <c r="S11" s="77"/>
+      <c r="R11" s="84"/>
+      <c r="S11" s="72"/>
       <c r="T11" s="27"/>
       <c r="U11" s="27"/>
     </row>
     <row r="12" spans="2:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K12" s="54"/>
+      <c r="K12" s="49"/>
       <c r="L12" s="27"/>
       <c r="M12" s="27"/>
       <c r="N12" s="27"/>
@@ -12297,55 +12335,55 @@
       <c r="U12" s="27"/>
     </row>
     <row r="13" spans="2:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="56"/>
-      <c r="D13" s="57" t="s">
-        <v>47</v>
+      <c r="C13" s="51"/>
+      <c r="D13" s="52" t="s">
+        <v>62</v>
       </c>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="59"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="54"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="55"/>
+      <c r="K13" s="50"/>
       <c r="L13" s="28"/>
       <c r="M13" s="28"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="78" t="s">
-        <v>47</v>
+      <c r="N13" s="65"/>
+      <c r="O13" s="73" t="s">
+        <v>62</v>
       </c>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="72"/>
+      <c r="P13" s="66"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="67"/>
       <c r="T13" s="27"/>
       <c r="U13" s="27"/>
     </row>
     <row r="14" spans="2:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="64"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="85" t="s">
+      <c r="C14" s="59"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="86"/>
-      <c r="H14" s="67"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="62"/>
       <c r="J14" s="8"/>
-      <c r="K14" s="55"/>
+      <c r="K14" s="50"/>
       <c r="L14" s="28"/>
       <c r="M14" s="28"/>
-      <c r="N14" s="75"/>
-      <c r="O14" s="87"/>
-      <c r="P14" s="76"/>
-      <c r="Q14" s="88" t="s">
+      <c r="N14" s="70"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="R14" s="89"/>
-      <c r="S14" s="77"/>
+      <c r="R14" s="84"/>
+      <c r="S14" s="72"/>
       <c r="T14" s="27"/>
       <c r="U14" s="27"/>
     </row>
     <row r="15" spans="2:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K15" s="54"/>
+      <c r="K15" s="49"/>
       <c r="L15" s="27"/>
       <c r="M15" s="27"/>
       <c r="N15" s="27"/>
@@ -12358,55 +12396,55 @@
       <c r="U15" s="27"/>
     </row>
     <row r="16" spans="2:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="56"/>
-      <c r="D16" s="57" t="s">
-        <v>48</v>
+      <c r="C16" s="51"/>
+      <c r="D16" s="52" t="s">
+        <v>61</v>
       </c>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="59"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="54"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="55"/>
+      <c r="K16" s="50"/>
       <c r="L16" s="28"/>
       <c r="M16" s="28"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="78" t="s">
-        <v>48</v>
+      <c r="N16" s="65"/>
+      <c r="O16" s="73" t="s">
+        <v>61</v>
       </c>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="72"/>
+      <c r="P16" s="66"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="67"/>
       <c r="T16" s="27"/>
       <c r="U16" s="27"/>
     </row>
     <row r="17" spans="3:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="64"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="85" t="s">
+      <c r="C17" s="59"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="86"/>
-      <c r="H17" s="67"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="62"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="55"/>
+      <c r="K17" s="50"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
-      <c r="N17" s="75"/>
-      <c r="O17" s="87"/>
-      <c r="P17" s="76"/>
-      <c r="Q17" s="88" t="s">
+      <c r="N17" s="70"/>
+      <c r="O17" s="82"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="R17" s="89"/>
-      <c r="S17" s="77"/>
+      <c r="R17" s="84"/>
+      <c r="S17" s="72"/>
       <c r="T17" s="27"/>
       <c r="U17" s="27"/>
     </row>
     <row r="18" spans="3:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K18" s="54"/>
+      <c r="K18" s="49"/>
       <c r="L18" s="27"/>
       <c r="M18" s="27"/>
       <c r="N18" s="27"/>
@@ -12419,55 +12457,55 @@
       <c r="U18" s="27"/>
     </row>
     <row r="19" spans="3:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="56"/>
-      <c r="D19" s="57" t="s">
-        <v>49</v>
+      <c r="C19" s="51"/>
+      <c r="D19" s="52" t="s">
+        <v>60</v>
       </c>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="59"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="54"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="55"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="28"/>
       <c r="M19" s="28"/>
-      <c r="N19" s="70"/>
-      <c r="O19" s="78" t="s">
-        <v>49</v>
+      <c r="N19" s="65"/>
+      <c r="O19" s="73" t="s">
+        <v>60</v>
       </c>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="72"/>
+      <c r="P19" s="66"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="66"/>
+      <c r="S19" s="67"/>
       <c r="T19" s="27"/>
       <c r="U19" s="27"/>
     </row>
     <row r="20" spans="3:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="64"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="85" t="s">
+      <c r="C20" s="59"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="G20" s="86"/>
-      <c r="H20" s="67"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="62"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="55"/>
+      <c r="K20" s="50"/>
       <c r="L20" s="28"/>
       <c r="M20" s="28"/>
-      <c r="N20" s="75"/>
-      <c r="O20" s="87"/>
-      <c r="P20" s="76"/>
-      <c r="Q20" s="88" t="s">
+      <c r="N20" s="70"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="R20" s="89"/>
-      <c r="S20" s="77"/>
+      <c r="R20" s="84"/>
+      <c r="S20" s="72"/>
       <c r="T20" s="27"/>
       <c r="U20" s="27"/>
     </row>
     <row r="21" spans="3:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K21" s="54"/>
+      <c r="K21" s="49"/>
       <c r="L21" s="27"/>
       <c r="M21" s="27"/>
       <c r="N21" s="27"/>
@@ -12480,57 +12518,57 @@
       <c r="U21" s="27"/>
     </row>
     <row r="22" spans="3:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="56"/>
-      <c r="D22" s="57" t="s">
-        <v>52</v>
+      <c r="C22" s="51"/>
+      <c r="D22" s="102" t="s">
+        <v>63</v>
       </c>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="59"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="8"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="55"/>
+      <c r="K22" s="50"/>
       <c r="L22" s="28"/>
       <c r="M22" s="28"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="78" t="s">
-        <v>52</v>
+      <c r="N22" s="65"/>
+      <c r="O22" s="105" t="s">
+        <v>65</v>
       </c>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-      <c r="T22" s="72"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="27"/>
       <c r="U22" s="27"/>
     </row>
     <row r="23" spans="3:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="64"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="85" t="s">
+      <c r="C23" s="59"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="G23" s="86"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="67"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="8"/>
       <c r="J23" s="8"/>
-      <c r="K23" s="55"/>
+      <c r="K23" s="50"/>
       <c r="L23" s="28"/>
       <c r="M23" s="28"/>
-      <c r="N23" s="75"/>
-      <c r="O23" s="87"/>
-      <c r="P23" s="76"/>
-      <c r="Q23" s="88" t="s">
+      <c r="N23" s="70"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="R23" s="89"/>
-      <c r="S23" s="89"/>
-      <c r="T23" s="77"/>
+      <c r="R23" s="84"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="27"/>
       <c r="U23" s="27"/>
     </row>
     <row r="24" spans="3:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K24" s="54"/>
+      <c r="K24" s="49"/>
       <c r="L24" s="27"/>
       <c r="M24" s="27"/>
       <c r="N24" s="27"/>
@@ -12543,57 +12581,57 @@
       <c r="U24" s="27"/>
     </row>
     <row r="25" spans="3:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="56"/>
-      <c r="D25" s="57" t="s">
-        <v>50</v>
+      <c r="C25" s="51"/>
+      <c r="D25" s="103" t="s">
+        <v>64</v>
       </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="59"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="8"/>
       <c r="J25" s="8"/>
-      <c r="K25" s="55"/>
+      <c r="K25" s="50"/>
       <c r="L25" s="28"/>
       <c r="M25" s="28"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="78" t="s">
-        <v>50</v>
+      <c r="N25" s="65"/>
+      <c r="O25" s="104" t="s">
+        <v>44</v>
       </c>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="71"/>
-      <c r="T25" s="72"/>
+      <c r="P25" s="66"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="27"/>
       <c r="U25" s="27"/>
     </row>
     <row r="26" spans="3:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="64"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="85" t="s">
+      <c r="C26" s="59"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="G26" s="86"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="67"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="55"/>
+      <c r="K26" s="50"/>
       <c r="L26" s="28"/>
       <c r="M26" s="28"/>
-      <c r="N26" s="75"/>
-      <c r="O26" s="87"/>
-      <c r="P26" s="76"/>
-      <c r="Q26" s="88" t="s">
+      <c r="N26" s="70"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="R26" s="89"/>
-      <c r="S26" s="89"/>
-      <c r="T26" s="77"/>
+      <c r="R26" s="84"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="27"/>
       <c r="U26" s="27"/>
     </row>
     <row r="27" spans="3:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K27" s="54"/>
+      <c r="K27" s="49"/>
       <c r="L27" s="27"/>
       <c r="M27" s="27"/>
       <c r="N27" s="27"/>
@@ -12606,55 +12644,55 @@
       <c r="U27" s="27"/>
     </row>
     <row r="28" spans="3:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="56"/>
-      <c r="D28" s="57" t="s">
-        <v>51</v>
+      <c r="C28" s="51"/>
+      <c r="D28" s="52" t="s">
+        <v>45</v>
       </c>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="59"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="54"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="55"/>
+      <c r="K28" s="50"/>
       <c r="L28" s="28"/>
       <c r="M28" s="28"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="78" t="s">
-        <v>51</v>
+      <c r="N28" s="65"/>
+      <c r="O28" s="73" t="s">
+        <v>45</v>
       </c>
-      <c r="P28" s="71"/>
-      <c r="Q28" s="71"/>
-      <c r="R28" s="71"/>
-      <c r="S28" s="72"/>
+      <c r="P28" s="66"/>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="67"/>
       <c r="T28" s="27"/>
       <c r="U28" s="27"/>
     </row>
     <row r="29" spans="3:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="64"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="85" t="s">
+      <c r="C29" s="59"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="G29" s="86"/>
-      <c r="H29" s="67"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="62"/>
       <c r="J29" s="8"/>
-      <c r="K29" s="55"/>
+      <c r="K29" s="50"/>
       <c r="L29" s="28"/>
       <c r="M29" s="28"/>
-      <c r="N29" s="75"/>
-      <c r="O29" s="87"/>
-      <c r="P29" s="76"/>
-      <c r="Q29" s="88" t="s">
+      <c r="N29" s="70"/>
+      <c r="O29" s="82"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="R29" s="89"/>
-      <c r="S29" s="77"/>
+      <c r="R29" s="84"/>
+      <c r="S29" s="72"/>
       <c r="T29" s="27"/>
       <c r="U29" s="27"/>
     </row>
     <row r="30" spans="3:21" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="K30" s="54"/>
+      <c r="K30" s="49"/>
       <c r="L30" s="27"/>
       <c r="M30" s="27"/>
       <c r="N30" s="27"/>
@@ -12667,7 +12705,7 @@
       <c r="U30" s="27"/>
     </row>
     <row r="31" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="K31" s="54"/>
+      <c r="K31" s="49"/>
       <c r="L31" s="27"/>
       <c r="M31" s="27"/>
       <c r="N31" s="27"/>
@@ -12680,7 +12718,7 @@
       <c r="U31" s="27"/>
     </row>
     <row r="32" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="K32" s="54"/>
+      <c r="K32" s="49"/>
       <c r="L32" s="27"/>
       <c r="M32" s="27"/>
       <c r="N32" s="27"/>
@@ -12693,7 +12731,7 @@
       <c r="U32" s="27"/>
     </row>
     <row r="33" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K33" s="54"/>
+      <c r="K33" s="49"/>
       <c r="L33" s="27"/>
       <c r="M33" s="27"/>
       <c r="N33" s="27"/>
@@ -12706,7 +12744,7 @@
       <c r="U33" s="27"/>
     </row>
     <row r="34" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K34" s="54"/>
+      <c r="K34" s="49"/>
       <c r="L34" s="27"/>
       <c r="M34" s="27"/>
       <c r="N34" s="27"/>
@@ -12719,7 +12757,7 @@
       <c r="U34" s="27"/>
     </row>
     <row r="35" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K35" s="54"/>
+      <c r="K35" s="49"/>
       <c r="L35" s="27"/>
       <c r="M35" s="27"/>
       <c r="N35" s="27"/>
@@ -12732,7 +12770,7 @@
       <c r="U35" s="27"/>
     </row>
     <row r="36" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K36" s="54"/>
+      <c r="K36" s="49"/>
       <c r="L36" s="27"/>
       <c r="M36" s="27"/>
       <c r="N36" s="27"/>
@@ -12745,7 +12783,7 @@
       <c r="U36" s="27"/>
     </row>
     <row r="37" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K37" s="54"/>
+      <c r="K37" s="49"/>
       <c r="L37" s="27"/>
       <c r="M37" s="27"/>
       <c r="N37" s="27"/>
@@ -12758,7 +12796,7 @@
       <c r="U37" s="27"/>
     </row>
     <row r="38" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K38" s="54"/>
+      <c r="K38" s="49"/>
       <c r="L38" s="27"/>
       <c r="M38" s="27"/>
       <c r="N38" s="27"/>
@@ -12771,7 +12809,7 @@
       <c r="U38" s="27"/>
     </row>
     <row r="39" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K39" s="54"/>
+      <c r="K39" s="49"/>
       <c r="L39" s="27"/>
       <c r="M39" s="27"/>
       <c r="N39" s="27"/>
@@ -12784,7 +12822,7 @@
       <c r="U39" s="27"/>
     </row>
     <row r="40" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K40" s="54"/>
+      <c r="K40" s="49"/>
       <c r="L40" s="27"/>
       <c r="M40" s="27"/>
       <c r="N40" s="27"/>
@@ -12797,7 +12835,7 @@
       <c r="U40" s="27"/>
     </row>
     <row r="41" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K41" s="54"/>
+      <c r="K41" s="49"/>
       <c r="L41" s="27"/>
       <c r="M41" s="27"/>
       <c r="N41" s="27"/>
@@ -12810,7 +12848,7 @@
       <c r="U41" s="27"/>
     </row>
     <row r="42" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K42" s="54"/>
+      <c r="K42" s="49"/>
       <c r="L42" s="27"/>
       <c r="M42" s="27"/>
       <c r="N42" s="27"/>
@@ -12823,7 +12861,7 @@
       <c r="U42" s="27"/>
     </row>
     <row r="43" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K43" s="54"/>
+      <c r="K43" s="49"/>
       <c r="L43" s="27"/>
       <c r="M43" s="27"/>
       <c r="N43" s="27"/>
@@ -12836,7 +12874,7 @@
       <c r="U43" s="27"/>
     </row>
     <row r="44" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K44" s="54"/>
+      <c r="K44" s="49"/>
       <c r="L44" s="27"/>
       <c r="M44" s="27"/>
       <c r="N44" s="27"/>
@@ -12849,7 +12887,7 @@
       <c r="U44" s="27"/>
     </row>
     <row r="45" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K45" s="54"/>
+      <c r="K45" s="49"/>
       <c r="L45" s="27"/>
       <c r="M45" s="27"/>
       <c r="N45" s="27"/>
@@ -12862,7 +12900,7 @@
       <c r="U45" s="27"/>
     </row>
     <row r="46" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K46" s="54"/>
+      <c r="K46" s="49"/>
       <c r="L46" s="27"/>
       <c r="M46" s="27"/>
       <c r="N46" s="27"/>
@@ -12875,7 +12913,7 @@
       <c r="U46" s="27"/>
     </row>
     <row r="47" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K47" s="54"/>
+      <c r="K47" s="49"/>
       <c r="L47" s="27"/>
       <c r="M47" s="27"/>
       <c r="N47" s="27"/>
@@ -12888,7 +12926,7 @@
       <c r="U47" s="27"/>
     </row>
     <row r="48" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K48" s="54"/>
+      <c r="K48" s="49"/>
       <c r="L48" s="27"/>
       <c r="M48" s="27"/>
       <c r="N48" s="27"/>
@@ -12901,7 +12939,7 @@
       <c r="U48" s="27"/>
     </row>
     <row r="49" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K49" s="54"/>
+      <c r="K49" s="49"/>
       <c r="L49" s="27"/>
       <c r="M49" s="27"/>
       <c r="N49" s="27"/>
@@ -12914,7 +12952,7 @@
       <c r="U49" s="27"/>
     </row>
     <row r="50" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K50" s="54"/>
+      <c r="K50" s="49"/>
       <c r="L50" s="27"/>
       <c r="M50" s="27"/>
       <c r="N50" s="27"/>
@@ -12927,7 +12965,7 @@
       <c r="U50" s="27"/>
     </row>
     <row r="51" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K51" s="54"/>
+      <c r="K51" s="49"/>
       <c r="L51" s="27"/>
       <c r="M51" s="27"/>
       <c r="N51" s="27"/>
@@ -12940,7 +12978,7 @@
       <c r="U51" s="27"/>
     </row>
     <row r="52" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K52" s="54"/>
+      <c r="K52" s="49"/>
       <c r="L52" s="27"/>
       <c r="M52" s="27"/>
       <c r="N52" s="27"/>
@@ -12953,7 +12991,7 @@
       <c r="U52" s="27"/>
     </row>
     <row r="53" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K53" s="54"/>
+      <c r="K53" s="49"/>
       <c r="L53" s="27"/>
       <c r="M53" s="27"/>
       <c r="N53" s="27"/>
@@ -12966,7 +13004,7 @@
       <c r="U53" s="27"/>
     </row>
     <row r="54" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K54" s="54"/>
+      <c r="K54" s="49"/>
       <c r="L54" s="27"/>
       <c r="M54" s="27"/>
       <c r="N54" s="27"/>
@@ -12979,7 +13017,7 @@
       <c r="U54" s="27"/>
     </row>
     <row r="55" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K55" s="54"/>
+      <c r="K55" s="49"/>
       <c r="L55" s="27"/>
       <c r="M55" s="27"/>
       <c r="N55" s="27"/>
@@ -12992,7 +13030,7 @@
       <c r="U55" s="27"/>
     </row>
     <row r="56" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K56" s="54"/>
+      <c r="K56" s="49"/>
       <c r="L56" s="27"/>
       <c r="M56" s="27"/>
       <c r="N56" s="27"/>
@@ -13005,7 +13043,7 @@
       <c r="U56" s="27"/>
     </row>
     <row r="57" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K57" s="54"/>
+      <c r="K57" s="49"/>
       <c r="L57" s="27"/>
       <c r="M57" s="27"/>
       <c r="N57" s="27"/>
@@ -13018,7 +13056,7 @@
       <c r="U57" s="27"/>
     </row>
     <row r="58" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K58" s="54"/>
+      <c r="K58" s="49"/>
       <c r="L58" s="27"/>
       <c r="M58" s="27"/>
       <c r="N58" s="27"/>
@@ -13031,7 +13069,7 @@
       <c r="U58" s="27"/>
     </row>
     <row r="59" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K59" s="54"/>
+      <c r="K59" s="49"/>
       <c r="L59" s="27"/>
       <c r="M59" s="27"/>
       <c r="N59" s="27"/>
@@ -13044,7 +13082,7 @@
       <c r="U59" s="27"/>
     </row>
     <row r="60" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K60" s="54"/>
+      <c r="K60" s="49"/>
       <c r="L60" s="27"/>
       <c r="M60" s="27"/>
       <c r="N60" s="27"/>
@@ -13057,7 +13095,7 @@
       <c r="U60" s="27"/>
     </row>
     <row r="61" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K61" s="54"/>
+      <c r="K61" s="49"/>
       <c r="L61" s="27"/>
       <c r="M61" s="27"/>
       <c r="N61" s="27"/>
@@ -13070,7 +13108,7 @@
       <c r="U61" s="27"/>
     </row>
     <row r="62" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K62" s="54"/>
+      <c r="K62" s="49"/>
       <c r="L62" s="27"/>
       <c r="M62" s="27"/>
       <c r="N62" s="27"/>
@@ -13083,7 +13121,7 @@
       <c r="U62" s="27"/>
     </row>
     <row r="63" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K63" s="54"/>
+      <c r="K63" s="49"/>
       <c r="L63" s="27"/>
       <c r="M63" s="27"/>
       <c r="N63" s="27"/>
@@ -13096,7 +13134,7 @@
       <c r="U63" s="27"/>
     </row>
     <row r="64" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K64" s="54"/>
+      <c r="K64" s="49"/>
       <c r="L64" s="27"/>
       <c r="M64" s="27"/>
       <c r="N64" s="27"/>
@@ -13109,7 +13147,7 @@
       <c r="U64" s="27"/>
     </row>
     <row r="65" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K65" s="54"/>
+      <c r="K65" s="49"/>
       <c r="L65" s="27"/>
       <c r="M65" s="27"/>
       <c r="N65" s="27"/>
@@ -13122,7 +13160,7 @@
       <c r="U65" s="27"/>
     </row>
     <row r="66" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K66" s="54"/>
+      <c r="K66" s="49"/>
       <c r="L66" s="27"/>
       <c r="M66" s="27"/>
       <c r="N66" s="27"/>
@@ -13135,7 +13173,7 @@
       <c r="U66" s="27"/>
     </row>
     <row r="67" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K67" s="54"/>
+      <c r="K67" s="49"/>
       <c r="L67" s="27"/>
       <c r="M67" s="27"/>
       <c r="N67" s="27"/>
@@ -13148,7 +13186,7 @@
       <c r="U67" s="27"/>
     </row>
     <row r="68" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K68" s="54"/>
+      <c r="K68" s="49"/>
       <c r="L68" s="27"/>
       <c r="M68" s="27"/>
       <c r="N68" s="27"/>
@@ -13161,7 +13199,7 @@
       <c r="U68" s="27"/>
     </row>
     <row r="69" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K69" s="54"/>
+      <c r="K69" s="49"/>
       <c r="L69" s="27"/>
       <c r="M69" s="27"/>
       <c r="N69" s="27"/>
@@ -13174,7 +13212,7 @@
       <c r="U69" s="27"/>
     </row>
     <row r="70" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K70" s="54"/>
+      <c r="K70" s="49"/>
       <c r="L70" s="27"/>
       <c r="M70" s="27"/>
       <c r="N70" s="27"/>
@@ -13187,7 +13225,7 @@
       <c r="U70" s="27"/>
     </row>
     <row r="71" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K71" s="54"/>
+      <c r="K71" s="49"/>
       <c r="L71" s="27"/>
       <c r="M71" s="27"/>
       <c r="N71" s="27"/>
@@ -13200,7 +13238,7 @@
       <c r="U71" s="27"/>
     </row>
     <row r="72" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K72" s="54"/>
+      <c r="K72" s="49"/>
       <c r="L72" s="27"/>
       <c r="M72" s="27"/>
       <c r="N72" s="27"/>
@@ -13213,7 +13251,7 @@
       <c r="U72" s="27"/>
     </row>
     <row r="73" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K73" s="54"/>
+      <c r="K73" s="49"/>
       <c r="L73" s="27"/>
       <c r="M73" s="27"/>
       <c r="N73" s="27"/>
@@ -13226,7 +13264,7 @@
       <c r="U73" s="27"/>
     </row>
     <row r="74" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K74" s="54"/>
+      <c r="K74" s="49"/>
       <c r="L74" s="27"/>
       <c r="M74" s="27"/>
       <c r="N74" s="27"/>
@@ -13239,7 +13277,7 @@
       <c r="U74" s="27"/>
     </row>
     <row r="75" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K75" s="54"/>
+      <c r="K75" s="49"/>
       <c r="L75" s="27"/>
       <c r="M75" s="27"/>
       <c r="N75" s="27"/>
@@ -13252,7 +13290,7 @@
       <c r="U75" s="27"/>
     </row>
     <row r="76" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K76" s="54"/>
+      <c r="K76" s="49"/>
       <c r="L76" s="27"/>
       <c r="M76" s="27"/>
       <c r="N76" s="27"/>
@@ -13265,7 +13303,7 @@
       <c r="U76" s="27"/>
     </row>
     <row r="77" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K77" s="54"/>
+      <c r="K77" s="49"/>
       <c r="L77" s="27"/>
       <c r="M77" s="27"/>
       <c r="N77" s="27"/>
@@ -13278,7 +13316,7 @@
       <c r="U77" s="27"/>
     </row>
     <row r="78" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K78" s="54"/>
+      <c r="K78" s="49"/>
       <c r="L78" s="27"/>
       <c r="M78" s="27"/>
       <c r="N78" s="27"/>
@@ -13291,7 +13329,7 @@
       <c r="U78" s="27"/>
     </row>
     <row r="79" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K79" s="54"/>
+      <c r="K79" s="49"/>
       <c r="L79" s="27"/>
       <c r="M79" s="27"/>
       <c r="N79" s="27"/>
@@ -13304,7 +13342,7 @@
       <c r="U79" s="27"/>
     </row>
     <row r="80" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K80" s="54"/>
+      <c r="K80" s="49"/>
       <c r="L80" s="27"/>
       <c r="M80" s="27"/>
       <c r="N80" s="27"/>
@@ -13317,7 +13355,7 @@
       <c r="U80" s="27"/>
     </row>
     <row r="81" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K81" s="54"/>
+      <c r="K81" s="49"/>
       <c r="L81" s="27"/>
       <c r="M81" s="27"/>
       <c r="N81" s="27"/>
@@ -13330,7 +13368,7 @@
       <c r="U81" s="27"/>
     </row>
     <row r="82" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K82" s="54"/>
+      <c r="K82" s="49"/>
       <c r="L82" s="27"/>
       <c r="M82" s="27"/>
       <c r="N82" s="27"/>
@@ -13343,7 +13381,7 @@
       <c r="U82" s="27"/>
     </row>
     <row r="83" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K83" s="54"/>
+      <c r="K83" s="49"/>
       <c r="L83" s="27"/>
       <c r="M83" s="27"/>
       <c r="N83" s="27"/>
@@ -13356,7 +13394,7 @@
       <c r="U83" s="27"/>
     </row>
     <row r="84" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K84" s="54"/>
+      <c r="K84" s="49"/>
       <c r="L84" s="27"/>
       <c r="M84" s="27"/>
       <c r="N84" s="27"/>
@@ -13369,7 +13407,7 @@
       <c r="U84" s="27"/>
     </row>
     <row r="85" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K85" s="54"/>
+      <c r="K85" s="49"/>
       <c r="L85" s="27"/>
       <c r="M85" s="27"/>
       <c r="N85" s="27"/>
@@ -13382,7 +13420,7 @@
       <c r="U85" s="27"/>
     </row>
     <row r="86" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K86" s="54"/>
+      <c r="K86" s="49"/>
       <c r="L86" s="27"/>
       <c r="M86" s="27"/>
       <c r="N86" s="27"/>
@@ -13395,7 +13433,7 @@
       <c r="U86" s="27"/>
     </row>
     <row r="87" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K87" s="54"/>
+      <c r="K87" s="49"/>
       <c r="L87" s="27"/>
       <c r="M87" s="27"/>
       <c r="N87" s="27"/>
@@ -13408,7 +13446,7 @@
       <c r="U87" s="27"/>
     </row>
     <row r="88" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K88" s="54"/>
+      <c r="K88" s="49"/>
       <c r="L88" s="27"/>
       <c r="M88" s="27"/>
       <c r="N88" s="27"/>
@@ -13421,7 +13459,7 @@
       <c r="U88" s="27"/>
     </row>
     <row r="89" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K89" s="54"/>
+      <c r="K89" s="49"/>
       <c r="L89" s="27"/>
       <c r="M89" s="27"/>
       <c r="N89" s="27"/>
@@ -13434,7 +13472,7 @@
       <c r="U89" s="27"/>
     </row>
     <row r="90" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K90" s="54"/>
+      <c r="K90" s="49"/>
       <c r="L90" s="27"/>
       <c r="M90" s="27"/>
       <c r="N90" s="27"/>
@@ -13447,7 +13485,7 @@
       <c r="U90" s="27"/>
     </row>
     <row r="91" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K91" s="54"/>
+      <c r="K91" s="49"/>
       <c r="L91" s="27"/>
       <c r="M91" s="27"/>
       <c r="N91" s="27"/>
@@ -13460,7 +13498,7 @@
       <c r="U91" s="27"/>
     </row>
     <row r="92" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K92" s="54"/>
+      <c r="K92" s="49"/>
       <c r="L92" s="27"/>
       <c r="M92" s="27"/>
       <c r="N92" s="27"/>
@@ -13473,7 +13511,7 @@
       <c r="U92" s="27"/>
     </row>
     <row r="93" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K93" s="54"/>
+      <c r="K93" s="49"/>
       <c r="L93" s="27"/>
       <c r="M93" s="27"/>
       <c r="N93" s="27"/>
@@ -13486,7 +13524,7 @@
       <c r="U93" s="27"/>
     </row>
     <row r="94" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K94" s="54"/>
+      <c r="K94" s="49"/>
       <c r="L94" s="27"/>
       <c r="M94" s="27"/>
       <c r="N94" s="27"/>
@@ -13499,7 +13537,7 @@
       <c r="U94" s="27"/>
     </row>
     <row r="95" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K95" s="54"/>
+      <c r="K95" s="49"/>
       <c r="L95" s="27"/>
       <c r="M95" s="27"/>
       <c r="N95" s="27"/>
@@ -13512,7 +13550,7 @@
       <c r="U95" s="27"/>
     </row>
     <row r="96" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K96" s="54"/>
+      <c r="K96" s="49"/>
       <c r="L96" s="27"/>
       <c r="M96" s="27"/>
       <c r="N96" s="27"/>
@@ -13525,7 +13563,7 @@
       <c r="U96" s="27"/>
     </row>
     <row r="97" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K97" s="54"/>
+      <c r="K97" s="49"/>
       <c r="L97" s="27"/>
       <c r="M97" s="27"/>
       <c r="N97" s="27"/>
@@ -13538,7 +13576,7 @@
       <c r="U97" s="27"/>
     </row>
     <row r="98" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K98" s="54"/>
+      <c r="K98" s="49"/>
       <c r="L98" s="27"/>
       <c r="M98" s="27"/>
       <c r="N98" s="27"/>
@@ -13551,7 +13589,7 @@
       <c r="U98" s="27"/>
     </row>
     <row r="99" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K99" s="54"/>
+      <c r="K99" s="49"/>
       <c r="L99" s="27"/>
       <c r="M99" s="27"/>
       <c r="N99" s="27"/>
@@ -13564,7 +13602,7 @@
       <c r="U99" s="27"/>
     </row>
     <row r="100" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K100" s="54"/>
+      <c r="K100" s="49"/>
       <c r="L100" s="27"/>
       <c r="M100" s="27"/>
       <c r="N100" s="27"/>
@@ -13577,7 +13615,7 @@
       <c r="U100" s="27"/>
     </row>
     <row r="101" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K101" s="54"/>
+      <c r="K101" s="49"/>
       <c r="L101" s="27"/>
       <c r="M101" s="27"/>
       <c r="N101" s="27"/>
@@ -13590,7 +13628,7 @@
       <c r="U101" s="27"/>
     </row>
     <row r="102" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K102" s="54"/>
+      <c r="K102" s="49"/>
       <c r="L102" s="27"/>
       <c r="M102" s="27"/>
       <c r="N102" s="27"/>
@@ -13603,7 +13641,7 @@
       <c r="U102" s="27"/>
     </row>
     <row r="103" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K103" s="54"/>
+      <c r="K103" s="49"/>
       <c r="L103" s="27"/>
       <c r="M103" s="27"/>
       <c r="N103" s="27"/>
@@ -13616,7 +13654,7 @@
       <c r="U103" s="27"/>
     </row>
     <row r="104" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K104" s="54"/>
+      <c r="K104" s="49"/>
       <c r="L104" s="27"/>
       <c r="M104" s="27"/>
       <c r="N104" s="27"/>
@@ -13629,7 +13667,7 @@
       <c r="U104" s="27"/>
     </row>
     <row r="105" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K105" s="54"/>
+      <c r="K105" s="49"/>
       <c r="L105" s="27"/>
       <c r="M105" s="27"/>
       <c r="N105" s="27"/>
@@ -13642,7 +13680,7 @@
       <c r="U105" s="27"/>
     </row>
     <row r="106" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K106" s="54"/>
+      <c r="K106" s="49"/>
       <c r="L106" s="27"/>
       <c r="M106" s="27"/>
       <c r="N106" s="27"/>
@@ -13655,7 +13693,7 @@
       <c r="U106" s="27"/>
     </row>
     <row r="107" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K107" s="54"/>
+      <c r="K107" s="49"/>
       <c r="L107" s="27"/>
       <c r="M107" s="27"/>
       <c r="N107" s="27"/>
@@ -13668,7 +13706,7 @@
       <c r="U107" s="27"/>
     </row>
     <row r="108" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K108" s="54"/>
+      <c r="K108" s="49"/>
       <c r="L108" s="27"/>
       <c r="M108" s="27"/>
       <c r="N108" s="27"/>
@@ -13681,7 +13719,7 @@
       <c r="U108" s="27"/>
     </row>
     <row r="109" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K109" s="54"/>
+      <c r="K109" s="49"/>
       <c r="L109" s="27"/>
       <c r="M109" s="27"/>
       <c r="N109" s="27"/>
@@ -13694,7 +13732,7 @@
       <c r="U109" s="27"/>
     </row>
     <row r="110" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K110" s="54"/>
+      <c r="K110" s="49"/>
       <c r="L110" s="27"/>
       <c r="M110" s="27"/>
       <c r="N110" s="27"/>
@@ -13707,7 +13745,7 @@
       <c r="U110" s="27"/>
     </row>
     <row r="111" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K111" s="54"/>
+      <c r="K111" s="49"/>
       <c r="L111" s="27"/>
       <c r="M111" s="27"/>
       <c r="N111" s="27"/>
@@ -13720,7 +13758,7 @@
       <c r="U111" s="27"/>
     </row>
     <row r="112" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K112" s="54"/>
+      <c r="K112" s="49"/>
       <c r="L112" s="27"/>
       <c r="M112" s="27"/>
       <c r="N112" s="27"/>
@@ -13733,7 +13771,7 @@
       <c r="U112" s="27"/>
     </row>
     <row r="113" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K113" s="54"/>
+      <c r="K113" s="49"/>
       <c r="L113" s="27"/>
       <c r="M113" s="27"/>
       <c r="N113" s="27"/>
@@ -13746,7 +13784,7 @@
       <c r="U113" s="27"/>
     </row>
     <row r="114" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K114" s="54"/>
+      <c r="K114" s="49"/>
       <c r="L114" s="27"/>
       <c r="M114" s="27"/>
       <c r="N114" s="27"/>
@@ -13759,7 +13797,7 @@
       <c r="U114" s="27"/>
     </row>
     <row r="115" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K115" s="54"/>
+      <c r="K115" s="49"/>
       <c r="L115" s="27"/>
       <c r="M115" s="27"/>
       <c r="N115" s="27"/>
@@ -13772,7 +13810,7 @@
       <c r="U115" s="27"/>
     </row>
     <row r="116" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K116" s="54"/>
+      <c r="K116" s="49"/>
       <c r="L116" s="27"/>
       <c r="M116" s="27"/>
       <c r="N116" s="27"/>
@@ -13785,7 +13823,7 @@
       <c r="U116" s="27"/>
     </row>
     <row r="117" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K117" s="54"/>
+      <c r="K117" s="49"/>
       <c r="L117" s="27"/>
       <c r="M117" s="27"/>
       <c r="N117" s="27"/>
@@ -13798,7 +13836,7 @@
       <c r="U117" s="27"/>
     </row>
     <row r="118" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K118" s="54"/>
+      <c r="K118" s="49"/>
       <c r="L118" s="27"/>
       <c r="M118" s="27"/>
       <c r="N118" s="27"/>
@@ -13811,7 +13849,7 @@
       <c r="U118" s="27"/>
     </row>
     <row r="119" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K119" s="54"/>
+      <c r="K119" s="49"/>
       <c r="L119" s="27"/>
       <c r="M119" s="27"/>
       <c r="N119" s="27"/>
@@ -13824,7 +13862,7 @@
       <c r="U119" s="27"/>
     </row>
     <row r="120" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K120" s="54"/>
+      <c r="K120" s="49"/>
       <c r="L120" s="27"/>
       <c r="M120" s="27"/>
       <c r="N120" s="27"/>
@@ -13837,7 +13875,7 @@
       <c r="U120" s="27"/>
     </row>
     <row r="121" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K121" s="54"/>
+      <c r="K121" s="49"/>
       <c r="L121" s="27"/>
       <c r="M121" s="27"/>
       <c r="N121" s="27"/>
@@ -13850,7 +13888,7 @@
       <c r="U121" s="27"/>
     </row>
     <row r="122" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K122" s="54"/>
+      <c r="K122" s="49"/>
       <c r="L122" s="27"/>
       <c r="M122" s="27"/>
       <c r="N122" s="27"/>
@@ -13863,7 +13901,7 @@
       <c r="U122" s="27"/>
     </row>
     <row r="123" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K123" s="54"/>
+      <c r="K123" s="49"/>
       <c r="L123" s="27"/>
       <c r="M123" s="27"/>
       <c r="N123" s="27"/>
@@ -13876,7 +13914,7 @@
       <c r="U123" s="27"/>
     </row>
     <row r="124" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K124" s="54"/>
+      <c r="K124" s="49"/>
       <c r="L124" s="27"/>
       <c r="M124" s="27"/>
       <c r="N124" s="27"/>
@@ -13889,7 +13927,7 @@
       <c r="U124" s="27"/>
     </row>
     <row r="125" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K125" s="54"/>
+      <c r="K125" s="49"/>
       <c r="L125" s="27"/>
       <c r="M125" s="27"/>
       <c r="N125" s="27"/>
@@ -13902,7 +13940,7 @@
       <c r="U125" s="27"/>
     </row>
     <row r="126" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K126" s="54"/>
+      <c r="K126" s="49"/>
       <c r="L126" s="27"/>
       <c r="M126" s="27"/>
       <c r="N126" s="27"/>
@@ -13915,7 +13953,7 @@
       <c r="U126" s="27"/>
     </row>
     <row r="127" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K127" s="54"/>
+      <c r="K127" s="49"/>
       <c r="L127" s="27"/>
       <c r="M127" s="27"/>
       <c r="N127" s="27"/>
@@ -13928,7 +13966,7 @@
       <c r="U127" s="27"/>
     </row>
     <row r="128" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K128" s="54"/>
+      <c r="K128" s="49"/>
       <c r="L128" s="27"/>
       <c r="M128" s="27"/>
       <c r="N128" s="27"/>
@@ -13941,7 +13979,7 @@
       <c r="U128" s="27"/>
     </row>
     <row r="129" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K129" s="54"/>
+      <c r="K129" s="49"/>
       <c r="L129" s="27"/>
       <c r="M129" s="27"/>
       <c r="N129" s="27"/>
@@ -13954,7 +13992,7 @@
       <c r="U129" s="27"/>
     </row>
     <row r="130" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K130" s="54"/>
+      <c r="K130" s="49"/>
       <c r="L130" s="27"/>
       <c r="M130" s="27"/>
       <c r="N130" s="27"/>
@@ -13967,7 +14005,7 @@
       <c r="U130" s="27"/>
     </row>
     <row r="131" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K131" s="54"/>
+      <c r="K131" s="49"/>
       <c r="L131" s="27"/>
       <c r="M131" s="27"/>
       <c r="N131" s="27"/>
@@ -13980,7 +14018,7 @@
       <c r="U131" s="27"/>
     </row>
     <row r="132" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K132" s="54"/>
+      <c r="K132" s="49"/>
       <c r="L132" s="27"/>
       <c r="M132" s="27"/>
       <c r="N132" s="27"/>
@@ -13993,7 +14031,7 @@
       <c r="U132" s="27"/>
     </row>
     <row r="133" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K133" s="54"/>
+      <c r="K133" s="49"/>
       <c r="L133" s="27"/>
       <c r="M133" s="27"/>
       <c r="N133" s="27"/>
@@ -14006,7 +14044,7 @@
       <c r="U133" s="27"/>
     </row>
     <row r="134" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K134" s="54"/>
+      <c r="K134" s="49"/>
       <c r="L134" s="27"/>
       <c r="M134" s="27"/>
       <c r="N134" s="27"/>
@@ -14019,7 +14057,7 @@
       <c r="U134" s="27"/>
     </row>
     <row r="135" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K135" s="54"/>
+      <c r="K135" s="49"/>
       <c r="L135" s="27"/>
       <c r="M135" s="27"/>
       <c r="N135" s="27"/>
@@ -14032,7 +14070,7 @@
       <c r="U135" s="27"/>
     </row>
     <row r="136" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K136" s="54"/>
+      <c r="K136" s="49"/>
       <c r="L136" s="27"/>
       <c r="M136" s="27"/>
       <c r="N136" s="27"/>
@@ -14045,7 +14083,7 @@
       <c r="U136" s="27"/>
     </row>
     <row r="137" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K137" s="54"/>
+      <c r="K137" s="49"/>
       <c r="L137" s="27"/>
       <c r="M137" s="27"/>
       <c r="N137" s="27"/>
@@ -14058,7 +14096,7 @@
       <c r="U137" s="27"/>
     </row>
     <row r="138" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K138" s="54"/>
+      <c r="K138" s="49"/>
       <c r="L138" s="27"/>
       <c r="M138" s="27"/>
       <c r="N138" s="27"/>
@@ -14071,7 +14109,7 @@
       <c r="U138" s="27"/>
     </row>
     <row r="139" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K139" s="54"/>
+      <c r="K139" s="49"/>
       <c r="L139" s="27"/>
       <c r="M139" s="27"/>
       <c r="N139" s="27"/>
@@ -14084,7 +14122,7 @@
       <c r="U139" s="27"/>
     </row>
     <row r="140" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K140" s="54"/>
+      <c r="K140" s="49"/>
       <c r="L140" s="27"/>
       <c r="M140" s="27"/>
       <c r="N140" s="27"/>
@@ -14097,7 +14135,7 @@
       <c r="U140" s="27"/>
     </row>
     <row r="141" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K141" s="54"/>
+      <c r="K141" s="49"/>
       <c r="L141" s="27"/>
       <c r="M141" s="27"/>
       <c r="N141" s="27"/>
@@ -14110,7 +14148,7 @@
       <c r="U141" s="27"/>
     </row>
     <row r="142" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K142" s="54"/>
+      <c r="K142" s="49"/>
       <c r="L142" s="27"/>
       <c r="M142" s="27"/>
       <c r="N142" s="27"/>
@@ -14123,7 +14161,7 @@
       <c r="U142" s="27"/>
     </row>
     <row r="143" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K143" s="54"/>
+      <c r="K143" s="49"/>
       <c r="L143" s="27"/>
       <c r="M143" s="27"/>
       <c r="N143" s="27"/>
@@ -14136,7 +14174,7 @@
       <c r="U143" s="27"/>
     </row>
     <row r="144" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K144" s="54"/>
+      <c r="K144" s="49"/>
       <c r="L144" s="27"/>
       <c r="M144" s="27"/>
       <c r="N144" s="27"/>
@@ -14149,7 +14187,7 @@
       <c r="U144" s="27"/>
     </row>
     <row r="145" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K145" s="54"/>
+      <c r="K145" s="49"/>
       <c r="L145" s="27"/>
       <c r="M145" s="27"/>
       <c r="N145" s="27"/>
@@ -14162,7 +14200,7 @@
       <c r="U145" s="27"/>
     </row>
     <row r="146" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K146" s="54"/>
+      <c r="K146" s="49"/>
       <c r="L146" s="27"/>
       <c r="M146" s="27"/>
       <c r="N146" s="27"/>
@@ -14175,7 +14213,7 @@
       <c r="U146" s="27"/>
     </row>
     <row r="147" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K147" s="54"/>
+      <c r="K147" s="49"/>
       <c r="L147" s="27"/>
       <c r="M147" s="27"/>
       <c r="N147" s="27"/>
@@ -14188,7 +14226,7 @@
       <c r="U147" s="27"/>
     </row>
     <row r="148" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K148" s="54"/>
+      <c r="K148" s="49"/>
       <c r="L148" s="27"/>
       <c r="M148" s="27"/>
       <c r="N148" s="27"/>
@@ -14201,7 +14239,7 @@
       <c r="U148" s="27"/>
     </row>
     <row r="149" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K149" s="54"/>
+      <c r="K149" s="49"/>
       <c r="L149" s="27"/>
       <c r="M149" s="27"/>
       <c r="N149" s="27"/>
@@ -14214,7 +14252,7 @@
       <c r="U149" s="27"/>
     </row>
     <row r="150" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K150" s="54"/>
+      <c r="K150" s="49"/>
       <c r="L150" s="27"/>
       <c r="M150" s="27"/>
       <c r="N150" s="27"/>
@@ -14227,7 +14265,7 @@
       <c r="U150" s="27"/>
     </row>
     <row r="151" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K151" s="54"/>
+      <c r="K151" s="49"/>
       <c r="L151" s="27"/>
       <c r="M151" s="27"/>
       <c r="N151" s="27"/>
@@ -14240,7 +14278,7 @@
       <c r="U151" s="27"/>
     </row>
     <row r="152" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K152" s="54"/>
+      <c r="K152" s="49"/>
       <c r="L152" s="27"/>
       <c r="M152" s="27"/>
       <c r="N152" s="27"/>
@@ -14253,7 +14291,7 @@
       <c r="U152" s="27"/>
     </row>
     <row r="153" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K153" s="54"/>
+      <c r="K153" s="49"/>
       <c r="L153" s="27"/>
       <c r="M153" s="27"/>
       <c r="N153" s="27"/>
@@ -14266,7 +14304,7 @@
       <c r="U153" s="27"/>
     </row>
     <row r="154" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K154" s="54"/>
+      <c r="K154" s="49"/>
       <c r="L154" s="27"/>
       <c r="M154" s="27"/>
       <c r="N154" s="27"/>
@@ -14279,7 +14317,7 @@
       <c r="U154" s="27"/>
     </row>
     <row r="155" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K155" s="54"/>
+      <c r="K155" s="49"/>
       <c r="L155" s="27"/>
       <c r="M155" s="27"/>
       <c r="N155" s="27"/>
@@ -14292,7 +14330,7 @@
       <c r="U155" s="27"/>
     </row>
     <row r="156" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K156" s="54"/>
+      <c r="K156" s="49"/>
       <c r="L156" s="27"/>
       <c r="M156" s="27"/>
       <c r="N156" s="27"/>
@@ -14305,7 +14343,7 @@
       <c r="U156" s="27"/>
     </row>
     <row r="157" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K157" s="54"/>
+      <c r="K157" s="49"/>
       <c r="L157" s="27"/>
       <c r="M157" s="27"/>
       <c r="N157" s="27"/>
@@ -14318,7 +14356,7 @@
       <c r="U157" s="27"/>
     </row>
     <row r="158" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K158" s="54"/>
+      <c r="K158" s="49"/>
       <c r="L158" s="27"/>
       <c r="M158" s="27"/>
       <c r="N158" s="27"/>
@@ -14331,7 +14369,7 @@
       <c r="U158" s="27"/>
     </row>
     <row r="159" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K159" s="54"/>
+      <c r="K159" s="49"/>
       <c r="L159" s="27"/>
       <c r="M159" s="27"/>
       <c r="N159" s="27"/>
@@ -14357,6 +14395,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46676688-DF90-4664-BF6D-E5409599E202}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:R38"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14376,8 +14415,8 @@
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C3" s="53" t="s">
-        <v>42</v>
+      <c r="C3" s="48" t="s">
+        <v>39</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -14690,6 +14729,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1540268B-B206-4F4D-8979-E712B9521EA3}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:U159"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14704,21 +14744,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="B2" s="91" t="str" cm="1">
+      <c r="B2" s="86" t="str" cm="1">
         <f t="array" aca="1" ref="B2" ca="1">RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1)))</f>
         <v>parts</v>
       </c>
     </row>
     <row r="3" spans="2:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="90"/>
-      <c r="C3" s="53" t="s">
-        <v>45</v>
+      <c r="B3" s="85"/>
+      <c r="C3" s="48" t="s">
+        <v>42</v>
       </c>
-      <c r="K3" s="54"/>
+      <c r="K3" s="49"/>
       <c r="L3" s="27"/>
       <c r="M3" s="27"/>
       <c r="N3" s="10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O3" s="27"/>
       <c r="P3" s="27"/>
@@ -14731,7 +14771,7 @@
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C4" s="13"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="55"/>
+      <c r="K4" s="50"/>
       <c r="L4" s="28"/>
       <c r="M4" s="28"/>
       <c r="N4" s="28"/>
@@ -14743,39 +14783,39 @@
       <c r="T4" s="27"/>
       <c r="U4" s="27"/>
     </row>
-    <row r="5" spans="2:21" s="92" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="93"/>
-      <c r="E5" s="97" t="s">
-        <v>46</v>
+    <row r="5" spans="2:21" s="87" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="88"/>
+      <c r="E5" s="92" t="s">
+        <v>43</v>
       </c>
       <c r="J5" s="25"/>
-      <c r="K5" s="94"/>
-      <c r="L5" s="95"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="98"/>
-      <c r="O5" s="98"/>
-      <c r="P5" s="99" t="s">
-        <v>46</v>
+      <c r="K5" s="89"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="93"/>
+      <c r="P5" s="94" t="s">
+        <v>43</v>
       </c>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
-      <c r="T5" s="96"/>
-      <c r="U5" s="96"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
+      <c r="S5" s="91"/>
+      <c r="T5" s="91"/>
+      <c r="U5" s="91"/>
     </row>
     <row r="6" spans="2:21" ht="24" x14ac:dyDescent="0.25">
-      <c r="C6" s="93"/>
-      <c r="E6" s="97" t="s">
-        <v>46</v>
+      <c r="C6" s="88"/>
+      <c r="E6" s="92" t="s">
+        <v>43</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="55"/>
+      <c r="K6" s="50"/>
       <c r="L6" s="28"/>
       <c r="M6" s="28"/>
-      <c r="N6" s="98"/>
-      <c r="O6" s="100"/>
-      <c r="P6" s="99" t="s">
-        <v>46</v>
+      <c r="N6" s="93"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="94" t="s">
+        <v>43</v>
       </c>
       <c r="Q6" s="27"/>
       <c r="R6" s="27"/>
@@ -14785,7 +14825,7 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="J7" s="8"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="50"/>
       <c r="L7" s="28"/>
       <c r="M7" s="28"/>
       <c r="N7" s="27"/>
@@ -14799,7 +14839,7 @@
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="J8" s="8"/>
-      <c r="K8" s="55"/>
+      <c r="K8" s="50"/>
       <c r="L8" s="28"/>
       <c r="M8" s="28"/>
       <c r="N8" s="27"/>
@@ -14812,7 +14852,7 @@
       <c r="U8" s="27"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="K9" s="54"/>
+      <c r="K9" s="49"/>
       <c r="L9" s="27"/>
       <c r="M9" s="27"/>
       <c r="N9" s="27"/>
@@ -14826,7 +14866,7 @@
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="J10" s="8"/>
-      <c r="K10" s="55"/>
+      <c r="K10" s="50"/>
       <c r="L10" s="28"/>
       <c r="M10" s="28"/>
       <c r="N10" s="27"/>
@@ -14840,7 +14880,7 @@
     </row>
     <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J11" s="8"/>
-      <c r="K11" s="55"/>
+      <c r="K11" s="50"/>
       <c r="L11" s="28"/>
       <c r="M11" s="28"/>
       <c r="N11" s="27"/>
@@ -14852,26 +14892,26 @@
       <c r="T11" s="27"/>
       <c r="U11" s="27"/>
     </row>
-    <row r="12" spans="2:21" s="101" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="C12" s="104" t="s">
-        <v>55</v>
+    <row r="12" spans="2:21" s="96" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="C12" s="99" t="s">
+        <v>48</v>
       </c>
-      <c r="K12" s="102"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="105"/>
-      <c r="N12" s="105" t="s">
-        <v>56</v>
+      <c r="K12" s="97"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="100"/>
+      <c r="N12" s="100" t="s">
+        <v>49</v>
       </c>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103"/>
-      <c r="S12" s="103"/>
-      <c r="T12" s="103"/>
-      <c r="U12" s="103"/>
+      <c r="O12" s="98"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="K13" s="54"/>
+      <c r="K13" s="49"/>
       <c r="L13" s="27"/>
       <c r="M13" s="27"/>
       <c r="N13" s="27"/>
@@ -14884,7 +14924,7 @@
       <c r="U13" s="27"/>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="K14" s="54"/>
+      <c r="K14" s="49"/>
       <c r="L14" s="27"/>
       <c r="M14" s="27"/>
       <c r="N14" s="27"/>
@@ -14897,7 +14937,7 @@
       <c r="U14" s="27"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="K15" s="54"/>
+      <c r="K15" s="49"/>
       <c r="L15" s="27"/>
       <c r="M15" s="27"/>
       <c r="N15" s="27"/>
@@ -14910,24 +14950,24 @@
       <c r="U15" s="27"/>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="D16" s="53" t="s">
-        <v>66</v>
+      <c r="D16" s="48" t="s">
+        <v>59</v>
       </c>
-      <c r="G16" s="53" t="s">
-        <v>57</v>
+      <c r="G16" s="48" t="s">
+        <v>50</v>
       </c>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="K16" s="54"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="K16" s="49"/>
       <c r="L16" s="27"/>
       <c r="M16" s="27"/>
-      <c r="N16" s="106" t="s">
-        <v>66</v>
+      <c r="N16" s="101" t="s">
+        <v>59</v>
       </c>
-      <c r="O16" s="106"/>
-      <c r="P16" s="106"/>
-      <c r="Q16" s="106" t="s">
-        <v>57</v>
+      <c r="O16" s="101"/>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="101" t="s">
+        <v>50</v>
       </c>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
@@ -14935,24 +14975,24 @@
       <c r="U16" s="27"/>
     </row>
     <row r="17" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="D17" s="53" t="s">
-        <v>58</v>
+      <c r="D17" s="48" t="s">
+        <v>51</v>
       </c>
-      <c r="E17" s="53"/>
-      <c r="G17" s="53" t="s">
-        <v>59</v>
+      <c r="E17" s="48"/>
+      <c r="G17" s="48" t="s">
+        <v>52</v>
       </c>
-      <c r="H17" s="53"/>
-      <c r="K17" s="54"/>
+      <c r="H17" s="48"/>
+      <c r="K17" s="49"/>
       <c r="L17" s="27"/>
       <c r="M17" s="27"/>
-      <c r="N17" s="106" t="s">
-        <v>58</v>
+      <c r="N17" s="101" t="s">
+        <v>51</v>
       </c>
-      <c r="O17" s="106"/>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="106" t="s">
-        <v>59</v>
+      <c r="O17" s="101"/>
+      <c r="P17" s="101"/>
+      <c r="Q17" s="101" t="s">
+        <v>52</v>
       </c>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
@@ -14960,24 +15000,24 @@
       <c r="U17" s="27"/>
     </row>
     <row r="18" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="D18" s="53" t="s">
-        <v>60</v>
+      <c r="D18" s="48" t="s">
+        <v>53</v>
       </c>
-      <c r="E18" s="53"/>
-      <c r="G18" s="53" t="s">
-        <v>61</v>
+      <c r="E18" s="48"/>
+      <c r="G18" s="48" t="s">
+        <v>54</v>
       </c>
-      <c r="H18" s="53"/>
-      <c r="K18" s="54"/>
+      <c r="H18" s="48"/>
+      <c r="K18" s="49"/>
       <c r="L18" s="27"/>
       <c r="M18" s="27"/>
-      <c r="N18" s="106" t="s">
-        <v>60</v>
+      <c r="N18" s="101" t="s">
+        <v>53</v>
       </c>
-      <c r="O18" s="106"/>
-      <c r="P18" s="106"/>
-      <c r="Q18" s="106" t="s">
-        <v>61</v>
+      <c r="O18" s="101"/>
+      <c r="P18" s="101"/>
+      <c r="Q18" s="101" t="s">
+        <v>54</v>
       </c>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
@@ -14985,24 +15025,24 @@
       <c r="U18" s="27"/>
     </row>
     <row r="19" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="D19" s="53" t="s">
-        <v>62</v>
+      <c r="D19" s="48" t="s">
+        <v>55</v>
       </c>
-      <c r="E19" s="53"/>
-      <c r="G19" s="53" t="s">
-        <v>63</v>
+      <c r="E19" s="48"/>
+      <c r="G19" s="48" t="s">
+        <v>56</v>
       </c>
-      <c r="I19" s="53"/>
-      <c r="K19" s="54"/>
+      <c r="I19" s="48"/>
+      <c r="K19" s="49"/>
       <c r="L19" s="27"/>
       <c r="M19" s="27"/>
-      <c r="N19" s="106" t="s">
-        <v>62</v>
+      <c r="N19" s="101" t="s">
+        <v>55</v>
       </c>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="106" t="s">
-        <v>63</v>
+      <c r="O19" s="101"/>
+      <c r="P19" s="101"/>
+      <c r="Q19" s="101" t="s">
+        <v>56</v>
       </c>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
@@ -15010,24 +15050,24 @@
       <c r="U19" s="27"/>
     </row>
     <row r="20" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="D20" s="53" t="s">
-        <v>64</v>
+      <c r="D20" s="48" t="s">
+        <v>57</v>
       </c>
-      <c r="E20" s="53"/>
-      <c r="G20" s="53" t="s">
-        <v>65</v>
+      <c r="E20" s="48"/>
+      <c r="G20" s="48" t="s">
+        <v>58</v>
       </c>
-      <c r="H20" s="53"/>
-      <c r="K20" s="54"/>
+      <c r="H20" s="48"/>
+      <c r="K20" s="49"/>
       <c r="L20" s="27"/>
       <c r="M20" s="27"/>
-      <c r="N20" s="106" t="s">
-        <v>64</v>
+      <c r="N20" s="101" t="s">
+        <v>57</v>
       </c>
-      <c r="O20" s="106"/>
-      <c r="P20" s="106"/>
-      <c r="Q20" s="106" t="s">
-        <v>65</v>
+      <c r="O20" s="101"/>
+      <c r="P20" s="101"/>
+      <c r="Q20" s="101" t="s">
+        <v>58</v>
       </c>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
@@ -15035,13 +15075,13 @@
       <c r="U20" s="27"/>
     </row>
     <row r="21" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="K21" s="54"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="K21" s="49"/>
       <c r="L21" s="27"/>
       <c r="M21" s="27"/>
       <c r="N21" s="27"/>
@@ -15054,7 +15094,7 @@
       <c r="U21" s="27"/>
     </row>
     <row r="22" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K22" s="54"/>
+      <c r="K22" s="49"/>
       <c r="L22" s="27"/>
       <c r="M22" s="27"/>
       <c r="N22" s="27"/>
@@ -15067,7 +15107,7 @@
       <c r="U22" s="27"/>
     </row>
     <row r="23" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K23" s="54"/>
+      <c r="K23" s="49"/>
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
       <c r="N23" s="27"/>
@@ -15080,7 +15120,7 @@
       <c r="U23" s="27"/>
     </row>
     <row r="24" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K24" s="54"/>
+      <c r="K24" s="49"/>
       <c r="L24" s="27"/>
       <c r="M24" s="27"/>
       <c r="N24" s="27"/>
@@ -15093,7 +15133,7 @@
       <c r="U24" s="27"/>
     </row>
     <row r="25" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K25" s="54"/>
+      <c r="K25" s="49"/>
       <c r="L25" s="27"/>
       <c r="M25" s="27"/>
       <c r="N25" s="27"/>
@@ -15106,7 +15146,7 @@
       <c r="U25" s="27"/>
     </row>
     <row r="26" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K26" s="54"/>
+      <c r="K26" s="49"/>
       <c r="L26" s="27"/>
       <c r="M26" s="27"/>
       <c r="N26" s="27"/>
@@ -15119,7 +15159,7 @@
       <c r="U26" s="27"/>
     </row>
     <row r="27" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K27" s="54"/>
+      <c r="K27" s="49"/>
       <c r="L27" s="27"/>
       <c r="M27" s="27"/>
       <c r="N27" s="27"/>
@@ -15132,7 +15172,7 @@
       <c r="U27" s="27"/>
     </row>
     <row r="28" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K28" s="54"/>
+      <c r="K28" s="49"/>
       <c r="L28" s="27"/>
       <c r="M28" s="27"/>
       <c r="N28" s="27"/>
@@ -15145,7 +15185,7 @@
       <c r="U28" s="27"/>
     </row>
     <row r="29" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K29" s="54"/>
+      <c r="K29" s="49"/>
       <c r="L29" s="27"/>
       <c r="M29" s="27"/>
       <c r="N29" s="27"/>
@@ -15158,7 +15198,7 @@
       <c r="U29" s="27"/>
     </row>
     <row r="30" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K30" s="54"/>
+      <c r="K30" s="49"/>
       <c r="L30" s="27"/>
       <c r="M30" s="27"/>
       <c r="N30" s="27"/>
@@ -15171,7 +15211,7 @@
       <c r="U30" s="27"/>
     </row>
     <row r="31" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K31" s="54"/>
+      <c r="K31" s="49"/>
       <c r="L31" s="27"/>
       <c r="M31" s="27"/>
       <c r="N31" s="27"/>
@@ -15184,7 +15224,7 @@
       <c r="U31" s="27"/>
     </row>
     <row r="32" spans="4:21" x14ac:dyDescent="0.25">
-      <c r="K32" s="54"/>
+      <c r="K32" s="49"/>
       <c r="L32" s="27"/>
       <c r="M32" s="27"/>
       <c r="N32" s="27"/>
@@ -15197,7 +15237,7 @@
       <c r="U32" s="27"/>
     </row>
     <row r="33" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K33" s="54"/>
+      <c r="K33" s="49"/>
       <c r="L33" s="27"/>
       <c r="M33" s="27"/>
       <c r="N33" s="27"/>
@@ -15210,7 +15250,7 @@
       <c r="U33" s="27"/>
     </row>
     <row r="34" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K34" s="54"/>
+      <c r="K34" s="49"/>
       <c r="L34" s="27"/>
       <c r="M34" s="27"/>
       <c r="N34" s="27"/>
@@ -15223,7 +15263,7 @@
       <c r="U34" s="27"/>
     </row>
     <row r="35" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K35" s="54"/>
+      <c r="K35" s="49"/>
       <c r="L35" s="27"/>
       <c r="M35" s="27"/>
       <c r="N35" s="27"/>
@@ -15236,7 +15276,7 @@
       <c r="U35" s="27"/>
     </row>
     <row r="36" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K36" s="54"/>
+      <c r="K36" s="49"/>
       <c r="L36" s="27"/>
       <c r="M36" s="27"/>
       <c r="N36" s="27"/>
@@ -15249,7 +15289,7 @@
       <c r="U36" s="27"/>
     </row>
     <row r="37" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K37" s="54"/>
+      <c r="K37" s="49"/>
       <c r="L37" s="27"/>
       <c r="M37" s="27"/>
       <c r="N37" s="27"/>
@@ -15262,7 +15302,7 @@
       <c r="U37" s="27"/>
     </row>
     <row r="38" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K38" s="54"/>
+      <c r="K38" s="49"/>
       <c r="L38" s="27"/>
       <c r="M38" s="27"/>
       <c r="N38" s="27"/>
@@ -15275,7 +15315,7 @@
       <c r="U38" s="27"/>
     </row>
     <row r="39" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K39" s="54"/>
+      <c r="K39" s="49"/>
       <c r="L39" s="27"/>
       <c r="M39" s="27"/>
       <c r="N39" s="27"/>
@@ -15288,7 +15328,7 @@
       <c r="U39" s="27"/>
     </row>
     <row r="40" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K40" s="54"/>
+      <c r="K40" s="49"/>
       <c r="L40" s="27"/>
       <c r="M40" s="27"/>
       <c r="N40" s="27"/>
@@ -15301,7 +15341,7 @@
       <c r="U40" s="27"/>
     </row>
     <row r="41" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K41" s="54"/>
+      <c r="K41" s="49"/>
       <c r="L41" s="27"/>
       <c r="M41" s="27"/>
       <c r="N41" s="27"/>
@@ -15314,7 +15354,7 @@
       <c r="U41" s="27"/>
     </row>
     <row r="42" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K42" s="54"/>
+      <c r="K42" s="49"/>
       <c r="L42" s="27"/>
       <c r="M42" s="27"/>
       <c r="N42" s="27"/>
@@ -15327,7 +15367,7 @@
       <c r="U42" s="27"/>
     </row>
     <row r="43" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K43" s="54"/>
+      <c r="K43" s="49"/>
       <c r="L43" s="27"/>
       <c r="M43" s="27"/>
       <c r="N43" s="27"/>
@@ -15340,7 +15380,7 @@
       <c r="U43" s="27"/>
     </row>
     <row r="44" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K44" s="54"/>
+      <c r="K44" s="49"/>
       <c r="L44" s="27"/>
       <c r="M44" s="27"/>
       <c r="N44" s="27"/>
@@ -15353,7 +15393,7 @@
       <c r="U44" s="27"/>
     </row>
     <row r="45" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K45" s="54"/>
+      <c r="K45" s="49"/>
       <c r="L45" s="27"/>
       <c r="M45" s="27"/>
       <c r="N45" s="27"/>
@@ -15366,7 +15406,7 @@
       <c r="U45" s="27"/>
     </row>
     <row r="46" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K46" s="54"/>
+      <c r="K46" s="49"/>
       <c r="L46" s="27"/>
       <c r="M46" s="27"/>
       <c r="N46" s="27"/>
@@ -15379,7 +15419,7 @@
       <c r="U46" s="27"/>
     </row>
     <row r="47" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K47" s="54"/>
+      <c r="K47" s="49"/>
       <c r="L47" s="27"/>
       <c r="M47" s="27"/>
       <c r="N47" s="27"/>
@@ -15392,7 +15432,7 @@
       <c r="U47" s="27"/>
     </row>
     <row r="48" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K48" s="54"/>
+      <c r="K48" s="49"/>
       <c r="L48" s="27"/>
       <c r="M48" s="27"/>
       <c r="N48" s="27"/>
@@ -15405,7 +15445,7 @@
       <c r="U48" s="27"/>
     </row>
     <row r="49" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K49" s="54"/>
+      <c r="K49" s="49"/>
       <c r="L49" s="27"/>
       <c r="M49" s="27"/>
       <c r="N49" s="27"/>
@@ -15418,7 +15458,7 @@
       <c r="U49" s="27"/>
     </row>
     <row r="50" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K50" s="54"/>
+      <c r="K50" s="49"/>
       <c r="L50" s="27"/>
       <c r="M50" s="27"/>
       <c r="N50" s="27"/>
@@ -15431,7 +15471,7 @@
       <c r="U50" s="27"/>
     </row>
     <row r="51" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K51" s="54"/>
+      <c r="K51" s="49"/>
       <c r="L51" s="27"/>
       <c r="M51" s="27"/>
       <c r="N51" s="27"/>
@@ -15444,7 +15484,7 @@
       <c r="U51" s="27"/>
     </row>
     <row r="52" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K52" s="54"/>
+      <c r="K52" s="49"/>
       <c r="L52" s="27"/>
       <c r="M52" s="27"/>
       <c r="N52" s="27"/>
@@ -15457,7 +15497,7 @@
       <c r="U52" s="27"/>
     </row>
     <row r="53" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K53" s="54"/>
+      <c r="K53" s="49"/>
       <c r="L53" s="27"/>
       <c r="M53" s="27"/>
       <c r="N53" s="27"/>
@@ -15470,7 +15510,7 @@
       <c r="U53" s="27"/>
     </row>
     <row r="54" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K54" s="54"/>
+      <c r="K54" s="49"/>
       <c r="L54" s="27"/>
       <c r="M54" s="27"/>
       <c r="N54" s="27"/>
@@ -15483,7 +15523,7 @@
       <c r="U54" s="27"/>
     </row>
     <row r="55" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K55" s="54"/>
+      <c r="K55" s="49"/>
       <c r="L55" s="27"/>
       <c r="M55" s="27"/>
       <c r="N55" s="27"/>
@@ -15496,7 +15536,7 @@
       <c r="U55" s="27"/>
     </row>
     <row r="56" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K56" s="54"/>
+      <c r="K56" s="49"/>
       <c r="L56" s="27"/>
       <c r="M56" s="27"/>
       <c r="N56" s="27"/>
@@ -15509,7 +15549,7 @@
       <c r="U56" s="27"/>
     </row>
     <row r="57" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K57" s="54"/>
+      <c r="K57" s="49"/>
       <c r="L57" s="27"/>
       <c r="M57" s="27"/>
       <c r="N57" s="27"/>
@@ -15522,7 +15562,7 @@
       <c r="U57" s="27"/>
     </row>
     <row r="58" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K58" s="54"/>
+      <c r="K58" s="49"/>
       <c r="L58" s="27"/>
       <c r="M58" s="27"/>
       <c r="N58" s="27"/>
@@ -15535,7 +15575,7 @@
       <c r="U58" s="27"/>
     </row>
     <row r="59" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K59" s="54"/>
+      <c r="K59" s="49"/>
       <c r="L59" s="27"/>
       <c r="M59" s="27"/>
       <c r="N59" s="27"/>
@@ -15548,7 +15588,7 @@
       <c r="U59" s="27"/>
     </row>
     <row r="60" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K60" s="54"/>
+      <c r="K60" s="49"/>
       <c r="L60" s="27"/>
       <c r="M60" s="27"/>
       <c r="N60" s="27"/>
@@ -15561,7 +15601,7 @@
       <c r="U60" s="27"/>
     </row>
     <row r="61" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K61" s="54"/>
+      <c r="K61" s="49"/>
       <c r="L61" s="27"/>
       <c r="M61" s="27"/>
       <c r="N61" s="27"/>
@@ -15574,7 +15614,7 @@
       <c r="U61" s="27"/>
     </row>
     <row r="62" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K62" s="54"/>
+      <c r="K62" s="49"/>
       <c r="L62" s="27"/>
       <c r="M62" s="27"/>
       <c r="N62" s="27"/>
@@ -15587,7 +15627,7 @@
       <c r="U62" s="27"/>
     </row>
     <row r="63" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K63" s="54"/>
+      <c r="K63" s="49"/>
       <c r="L63" s="27"/>
       <c r="M63" s="27"/>
       <c r="N63" s="27"/>
@@ -15600,7 +15640,7 @@
       <c r="U63" s="27"/>
     </row>
     <row r="64" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K64" s="54"/>
+      <c r="K64" s="49"/>
       <c r="L64" s="27"/>
       <c r="M64" s="27"/>
       <c r="N64" s="27"/>
@@ -15613,7 +15653,7 @@
       <c r="U64" s="27"/>
     </row>
     <row r="65" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K65" s="54"/>
+      <c r="K65" s="49"/>
       <c r="L65" s="27"/>
       <c r="M65" s="27"/>
       <c r="N65" s="27"/>
@@ -15626,7 +15666,7 @@
       <c r="U65" s="27"/>
     </row>
     <row r="66" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K66" s="54"/>
+      <c r="K66" s="49"/>
       <c r="L66" s="27"/>
       <c r="M66" s="27"/>
       <c r="N66" s="27"/>
@@ -15639,7 +15679,7 @@
       <c r="U66" s="27"/>
     </row>
     <row r="67" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K67" s="54"/>
+      <c r="K67" s="49"/>
       <c r="L67" s="27"/>
       <c r="M67" s="27"/>
       <c r="N67" s="27"/>
@@ -15652,7 +15692,7 @@
       <c r="U67" s="27"/>
     </row>
     <row r="68" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K68" s="54"/>
+      <c r="K68" s="49"/>
       <c r="L68" s="27"/>
       <c r="M68" s="27"/>
       <c r="N68" s="27"/>
@@ -15665,7 +15705,7 @@
       <c r="U68" s="27"/>
     </row>
     <row r="69" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K69" s="54"/>
+      <c r="K69" s="49"/>
       <c r="L69" s="27"/>
       <c r="M69" s="27"/>
       <c r="N69" s="27"/>
@@ -15678,7 +15718,7 @@
       <c r="U69" s="27"/>
     </row>
     <row r="70" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K70" s="54"/>
+      <c r="K70" s="49"/>
       <c r="L70" s="27"/>
       <c r="M70" s="27"/>
       <c r="N70" s="27"/>
@@ -15691,7 +15731,7 @@
       <c r="U70" s="27"/>
     </row>
     <row r="71" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K71" s="54"/>
+      <c r="K71" s="49"/>
       <c r="L71" s="27"/>
       <c r="M71" s="27"/>
       <c r="N71" s="27"/>
@@ -15704,7 +15744,7 @@
       <c r="U71" s="27"/>
     </row>
     <row r="72" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K72" s="54"/>
+      <c r="K72" s="49"/>
       <c r="L72" s="27"/>
       <c r="M72" s="27"/>
       <c r="N72" s="27"/>
@@ -15717,7 +15757,7 @@
       <c r="U72" s="27"/>
     </row>
     <row r="73" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K73" s="54"/>
+      <c r="K73" s="49"/>
       <c r="L73" s="27"/>
       <c r="M73" s="27"/>
       <c r="N73" s="27"/>
@@ -15730,7 +15770,7 @@
       <c r="U73" s="27"/>
     </row>
     <row r="74" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K74" s="54"/>
+      <c r="K74" s="49"/>
       <c r="L74" s="27"/>
       <c r="M74" s="27"/>
       <c r="N74" s="27"/>
@@ -15743,7 +15783,7 @@
       <c r="U74" s="27"/>
     </row>
     <row r="75" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K75" s="54"/>
+      <c r="K75" s="49"/>
       <c r="L75" s="27"/>
       <c r="M75" s="27"/>
       <c r="N75" s="27"/>
@@ -15756,7 +15796,7 @@
       <c r="U75" s="27"/>
     </row>
     <row r="76" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K76" s="54"/>
+      <c r="K76" s="49"/>
       <c r="L76" s="27"/>
       <c r="M76" s="27"/>
       <c r="N76" s="27"/>
@@ -15769,7 +15809,7 @@
       <c r="U76" s="27"/>
     </row>
     <row r="77" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K77" s="54"/>
+      <c r="K77" s="49"/>
       <c r="L77" s="27"/>
       <c r="M77" s="27"/>
       <c r="N77" s="27"/>
@@ -15782,7 +15822,7 @@
       <c r="U77" s="27"/>
     </row>
     <row r="78" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K78" s="54"/>
+      <c r="K78" s="49"/>
       <c r="L78" s="27"/>
       <c r="M78" s="27"/>
       <c r="N78" s="27"/>
@@ -15795,7 +15835,7 @@
       <c r="U78" s="27"/>
     </row>
     <row r="79" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K79" s="54"/>
+      <c r="K79" s="49"/>
       <c r="L79" s="27"/>
       <c r="M79" s="27"/>
       <c r="N79" s="27"/>
@@ -15808,7 +15848,7 @@
       <c r="U79" s="27"/>
     </row>
     <row r="80" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K80" s="54"/>
+      <c r="K80" s="49"/>
       <c r="L80" s="27"/>
       <c r="M80" s="27"/>
       <c r="N80" s="27"/>
@@ -15821,7 +15861,7 @@
       <c r="U80" s="27"/>
     </row>
     <row r="81" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K81" s="54"/>
+      <c r="K81" s="49"/>
       <c r="L81" s="27"/>
       <c r="M81" s="27"/>
       <c r="N81" s="27"/>
@@ -15834,7 +15874,7 @@
       <c r="U81" s="27"/>
     </row>
     <row r="82" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K82" s="54"/>
+      <c r="K82" s="49"/>
       <c r="L82" s="27"/>
       <c r="M82" s="27"/>
       <c r="N82" s="27"/>
@@ -15847,7 +15887,7 @@
       <c r="U82" s="27"/>
     </row>
     <row r="83" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K83" s="54"/>
+      <c r="K83" s="49"/>
       <c r="L83" s="27"/>
       <c r="M83" s="27"/>
       <c r="N83" s="27"/>
@@ -15860,7 +15900,7 @@
       <c r="U83" s="27"/>
     </row>
     <row r="84" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K84" s="54"/>
+      <c r="K84" s="49"/>
       <c r="L84" s="27"/>
       <c r="M84" s="27"/>
       <c r="N84" s="27"/>
@@ -15873,7 +15913,7 @@
       <c r="U84" s="27"/>
     </row>
     <row r="85" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K85" s="54"/>
+      <c r="K85" s="49"/>
       <c r="L85" s="27"/>
       <c r="M85" s="27"/>
       <c r="N85" s="27"/>
@@ -15886,7 +15926,7 @@
       <c r="U85" s="27"/>
     </row>
     <row r="86" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K86" s="54"/>
+      <c r="K86" s="49"/>
       <c r="L86" s="27"/>
       <c r="M86" s="27"/>
       <c r="N86" s="27"/>
@@ -15899,7 +15939,7 @@
       <c r="U86" s="27"/>
     </row>
     <row r="87" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K87" s="54"/>
+      <c r="K87" s="49"/>
       <c r="L87" s="27"/>
       <c r="M87" s="27"/>
       <c r="N87" s="27"/>
@@ -15912,7 +15952,7 @@
       <c r="U87" s="27"/>
     </row>
     <row r="88" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K88" s="54"/>
+      <c r="K88" s="49"/>
       <c r="L88" s="27"/>
       <c r="M88" s="27"/>
       <c r="N88" s="27"/>
@@ -15925,7 +15965,7 @@
       <c r="U88" s="27"/>
     </row>
     <row r="89" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K89" s="54"/>
+      <c r="K89" s="49"/>
       <c r="L89" s="27"/>
       <c r="M89" s="27"/>
       <c r="N89" s="27"/>
@@ -15938,7 +15978,7 @@
       <c r="U89" s="27"/>
     </row>
     <row r="90" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K90" s="54"/>
+      <c r="K90" s="49"/>
       <c r="L90" s="27"/>
       <c r="M90" s="27"/>
       <c r="N90" s="27"/>
@@ -15951,7 +15991,7 @@
       <c r="U90" s="27"/>
     </row>
     <row r="91" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K91" s="54"/>
+      <c r="K91" s="49"/>
       <c r="L91" s="27"/>
       <c r="M91" s="27"/>
       <c r="N91" s="27"/>
@@ -15964,7 +16004,7 @@
       <c r="U91" s="27"/>
     </row>
     <row r="92" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K92" s="54"/>
+      <c r="K92" s="49"/>
       <c r="L92" s="27"/>
       <c r="M92" s="27"/>
       <c r="N92" s="27"/>
@@ -15977,7 +16017,7 @@
       <c r="U92" s="27"/>
     </row>
     <row r="93" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K93" s="54"/>
+      <c r="K93" s="49"/>
       <c r="L93" s="27"/>
       <c r="M93" s="27"/>
       <c r="N93" s="27"/>
@@ -15990,7 +16030,7 @@
       <c r="U93" s="27"/>
     </row>
     <row r="94" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K94" s="54"/>
+      <c r="K94" s="49"/>
       <c r="L94" s="27"/>
       <c r="M94" s="27"/>
       <c r="N94" s="27"/>
@@ -16003,7 +16043,7 @@
       <c r="U94" s="27"/>
     </row>
     <row r="95" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K95" s="54"/>
+      <c r="K95" s="49"/>
       <c r="L95" s="27"/>
       <c r="M95" s="27"/>
       <c r="N95" s="27"/>
@@ -16016,7 +16056,7 @@
       <c r="U95" s="27"/>
     </row>
     <row r="96" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K96" s="54"/>
+      <c r="K96" s="49"/>
       <c r="L96" s="27"/>
       <c r="M96" s="27"/>
       <c r="N96" s="27"/>
@@ -16029,7 +16069,7 @@
       <c r="U96" s="27"/>
     </row>
     <row r="97" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K97" s="54"/>
+      <c r="K97" s="49"/>
       <c r="L97" s="27"/>
       <c r="M97" s="27"/>
       <c r="N97" s="27"/>
@@ -16042,7 +16082,7 @@
       <c r="U97" s="27"/>
     </row>
     <row r="98" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K98" s="54"/>
+      <c r="K98" s="49"/>
       <c r="L98" s="27"/>
       <c r="M98" s="27"/>
       <c r="N98" s="27"/>
@@ -16055,7 +16095,7 @@
       <c r="U98" s="27"/>
     </row>
     <row r="99" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K99" s="54"/>
+      <c r="K99" s="49"/>
       <c r="L99" s="27"/>
       <c r="M99" s="27"/>
       <c r="N99" s="27"/>
@@ -16068,7 +16108,7 @@
       <c r="U99" s="27"/>
     </row>
     <row r="100" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K100" s="54"/>
+      <c r="K100" s="49"/>
       <c r="L100" s="27"/>
       <c r="M100" s="27"/>
       <c r="N100" s="27"/>
@@ -16081,7 +16121,7 @@
       <c r="U100" s="27"/>
     </row>
     <row r="101" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K101" s="54"/>
+      <c r="K101" s="49"/>
       <c r="L101" s="27"/>
       <c r="M101" s="27"/>
       <c r="N101" s="27"/>
@@ -16094,7 +16134,7 @@
       <c r="U101" s="27"/>
     </row>
     <row r="102" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K102" s="54"/>
+      <c r="K102" s="49"/>
       <c r="L102" s="27"/>
       <c r="M102" s="27"/>
       <c r="N102" s="27"/>
@@ -16107,7 +16147,7 @@
       <c r="U102" s="27"/>
     </row>
     <row r="103" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K103" s="54"/>
+      <c r="K103" s="49"/>
       <c r="L103" s="27"/>
       <c r="M103" s="27"/>
       <c r="N103" s="27"/>
@@ -16120,7 +16160,7 @@
       <c r="U103" s="27"/>
     </row>
     <row r="104" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K104" s="54"/>
+      <c r="K104" s="49"/>
       <c r="L104" s="27"/>
       <c r="M104" s="27"/>
       <c r="N104" s="27"/>
@@ -16133,7 +16173,7 @@
       <c r="U104" s="27"/>
     </row>
     <row r="105" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K105" s="54"/>
+      <c r="K105" s="49"/>
       <c r="L105" s="27"/>
       <c r="M105" s="27"/>
       <c r="N105" s="27"/>
@@ -16146,7 +16186,7 @@
       <c r="U105" s="27"/>
     </row>
     <row r="106" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K106" s="54"/>
+      <c r="K106" s="49"/>
       <c r="L106" s="27"/>
       <c r="M106" s="27"/>
       <c r="N106" s="27"/>
@@ -16159,7 +16199,7 @@
       <c r="U106" s="27"/>
     </row>
     <row r="107" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K107" s="54"/>
+      <c r="K107" s="49"/>
       <c r="L107" s="27"/>
       <c r="M107" s="27"/>
       <c r="N107" s="27"/>
@@ -16172,7 +16212,7 @@
       <c r="U107" s="27"/>
     </row>
     <row r="108" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K108" s="54"/>
+      <c r="K108" s="49"/>
       <c r="L108" s="27"/>
       <c r="M108" s="27"/>
       <c r="N108" s="27"/>
@@ -16185,7 +16225,7 @@
       <c r="U108" s="27"/>
     </row>
     <row r="109" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K109" s="54"/>
+      <c r="K109" s="49"/>
       <c r="L109" s="27"/>
       <c r="M109" s="27"/>
       <c r="N109" s="27"/>
@@ -16198,7 +16238,7 @@
       <c r="U109" s="27"/>
     </row>
     <row r="110" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K110" s="54"/>
+      <c r="K110" s="49"/>
       <c r="L110" s="27"/>
       <c r="M110" s="27"/>
       <c r="N110" s="27"/>
@@ -16211,7 +16251,7 @@
       <c r="U110" s="27"/>
     </row>
     <row r="111" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K111" s="54"/>
+      <c r="K111" s="49"/>
       <c r="L111" s="27"/>
       <c r="M111" s="27"/>
       <c r="N111" s="27"/>
@@ -16224,7 +16264,7 @@
       <c r="U111" s="27"/>
     </row>
     <row r="112" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K112" s="54"/>
+      <c r="K112" s="49"/>
       <c r="L112" s="27"/>
       <c r="M112" s="27"/>
       <c r="N112" s="27"/>
@@ -16237,7 +16277,7 @@
       <c r="U112" s="27"/>
     </row>
     <row r="113" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K113" s="54"/>
+      <c r="K113" s="49"/>
       <c r="L113" s="27"/>
       <c r="M113" s="27"/>
       <c r="N113" s="27"/>
@@ -16250,7 +16290,7 @@
       <c r="U113" s="27"/>
     </row>
     <row r="114" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K114" s="54"/>
+      <c r="K114" s="49"/>
       <c r="L114" s="27"/>
       <c r="M114" s="27"/>
       <c r="N114" s="27"/>
@@ -16263,7 +16303,7 @@
       <c r="U114" s="27"/>
     </row>
     <row r="115" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K115" s="54"/>
+      <c r="K115" s="49"/>
       <c r="L115" s="27"/>
       <c r="M115" s="27"/>
       <c r="N115" s="27"/>
@@ -16276,7 +16316,7 @@
       <c r="U115" s="27"/>
     </row>
     <row r="116" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K116" s="54"/>
+      <c r="K116" s="49"/>
       <c r="L116" s="27"/>
       <c r="M116" s="27"/>
       <c r="N116" s="27"/>
@@ -16289,7 +16329,7 @@
       <c r="U116" s="27"/>
     </row>
     <row r="117" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K117" s="54"/>
+      <c r="K117" s="49"/>
       <c r="L117" s="27"/>
       <c r="M117" s="27"/>
       <c r="N117" s="27"/>
@@ -16302,7 +16342,7 @@
       <c r="U117" s="27"/>
     </row>
     <row r="118" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K118" s="54"/>
+      <c r="K118" s="49"/>
       <c r="L118" s="27"/>
       <c r="M118" s="27"/>
       <c r="N118" s="27"/>
@@ -16315,7 +16355,7 @@
       <c r="U118" s="27"/>
     </row>
     <row r="119" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K119" s="54"/>
+      <c r="K119" s="49"/>
       <c r="L119" s="27"/>
       <c r="M119" s="27"/>
       <c r="N119" s="27"/>
@@ -16328,7 +16368,7 @@
       <c r="U119" s="27"/>
     </row>
     <row r="120" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K120" s="54"/>
+      <c r="K120" s="49"/>
       <c r="L120" s="27"/>
       <c r="M120" s="27"/>
       <c r="N120" s="27"/>
@@ -16341,7 +16381,7 @@
       <c r="U120" s="27"/>
     </row>
     <row r="121" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K121" s="54"/>
+      <c r="K121" s="49"/>
       <c r="L121" s="27"/>
       <c r="M121" s="27"/>
       <c r="N121" s="27"/>
@@ -16354,7 +16394,7 @@
       <c r="U121" s="27"/>
     </row>
     <row r="122" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K122" s="54"/>
+      <c r="K122" s="49"/>
       <c r="L122" s="27"/>
       <c r="M122" s="27"/>
       <c r="N122" s="27"/>
@@ -16367,7 +16407,7 @@
       <c r="U122" s="27"/>
     </row>
     <row r="123" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K123" s="54"/>
+      <c r="K123" s="49"/>
       <c r="L123" s="27"/>
       <c r="M123" s="27"/>
       <c r="N123" s="27"/>
@@ -16380,7 +16420,7 @@
       <c r="U123" s="27"/>
     </row>
     <row r="124" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K124" s="54"/>
+      <c r="K124" s="49"/>
       <c r="L124" s="27"/>
       <c r="M124" s="27"/>
       <c r="N124" s="27"/>
@@ -16393,7 +16433,7 @@
       <c r="U124" s="27"/>
     </row>
     <row r="125" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K125" s="54"/>
+      <c r="K125" s="49"/>
       <c r="L125" s="27"/>
       <c r="M125" s="27"/>
       <c r="N125" s="27"/>
@@ -16406,7 +16446,7 @@
       <c r="U125" s="27"/>
     </row>
     <row r="126" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K126" s="54"/>
+      <c r="K126" s="49"/>
       <c r="L126" s="27"/>
       <c r="M126" s="27"/>
       <c r="N126" s="27"/>
@@ -16419,7 +16459,7 @@
       <c r="U126" s="27"/>
     </row>
     <row r="127" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K127" s="54"/>
+      <c r="K127" s="49"/>
       <c r="L127" s="27"/>
       <c r="M127" s="27"/>
       <c r="N127" s="27"/>
@@ -16432,7 +16472,7 @@
       <c r="U127" s="27"/>
     </row>
     <row r="128" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K128" s="54"/>
+      <c r="K128" s="49"/>
       <c r="L128" s="27"/>
       <c r="M128" s="27"/>
       <c r="N128" s="27"/>
@@ -16445,7 +16485,7 @@
       <c r="U128" s="27"/>
     </row>
     <row r="129" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K129" s="54"/>
+      <c r="K129" s="49"/>
       <c r="L129" s="27"/>
       <c r="M129" s="27"/>
       <c r="N129" s="27"/>
@@ -16458,7 +16498,7 @@
       <c r="U129" s="27"/>
     </row>
     <row r="130" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K130" s="54"/>
+      <c r="K130" s="49"/>
       <c r="L130" s="27"/>
       <c r="M130" s="27"/>
       <c r="N130" s="27"/>
@@ -16471,7 +16511,7 @@
       <c r="U130" s="27"/>
     </row>
     <row r="131" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K131" s="54"/>
+      <c r="K131" s="49"/>
       <c r="L131" s="27"/>
       <c r="M131" s="27"/>
       <c r="N131" s="27"/>
@@ -16484,7 +16524,7 @@
       <c r="U131" s="27"/>
     </row>
     <row r="132" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K132" s="54"/>
+      <c r="K132" s="49"/>
       <c r="L132" s="27"/>
       <c r="M132" s="27"/>
       <c r="N132" s="27"/>
@@ -16497,7 +16537,7 @@
       <c r="U132" s="27"/>
     </row>
     <row r="133" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K133" s="54"/>
+      <c r="K133" s="49"/>
       <c r="L133" s="27"/>
       <c r="M133" s="27"/>
       <c r="N133" s="27"/>
@@ -16510,7 +16550,7 @@
       <c r="U133" s="27"/>
     </row>
     <row r="134" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K134" s="54"/>
+      <c r="K134" s="49"/>
       <c r="L134" s="27"/>
       <c r="M134" s="27"/>
       <c r="N134" s="27"/>
@@ -16523,7 +16563,7 @@
       <c r="U134" s="27"/>
     </row>
     <row r="135" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K135" s="54"/>
+      <c r="K135" s="49"/>
       <c r="L135" s="27"/>
       <c r="M135" s="27"/>
       <c r="N135" s="27"/>
@@ -16536,7 +16576,7 @@
       <c r="U135" s="27"/>
     </row>
     <row r="136" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K136" s="54"/>
+      <c r="K136" s="49"/>
       <c r="L136" s="27"/>
       <c r="M136" s="27"/>
       <c r="N136" s="27"/>
@@ -16549,7 +16589,7 @@
       <c r="U136" s="27"/>
     </row>
     <row r="137" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K137" s="54"/>
+      <c r="K137" s="49"/>
       <c r="L137" s="27"/>
       <c r="M137" s="27"/>
       <c r="N137" s="27"/>
@@ -16562,7 +16602,7 @@
       <c r="U137" s="27"/>
     </row>
     <row r="138" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K138" s="54"/>
+      <c r="K138" s="49"/>
       <c r="L138" s="27"/>
       <c r="M138" s="27"/>
       <c r="N138" s="27"/>
@@ -16575,7 +16615,7 @@
       <c r="U138" s="27"/>
     </row>
     <row r="139" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K139" s="54"/>
+      <c r="K139" s="49"/>
       <c r="L139" s="27"/>
       <c r="M139" s="27"/>
       <c r="N139" s="27"/>
@@ -16588,7 +16628,7 @@
       <c r="U139" s="27"/>
     </row>
     <row r="140" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K140" s="54"/>
+      <c r="K140" s="49"/>
       <c r="L140" s="27"/>
       <c r="M140" s="27"/>
       <c r="N140" s="27"/>
@@ -16601,7 +16641,7 @@
       <c r="U140" s="27"/>
     </row>
     <row r="141" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K141" s="54"/>
+      <c r="K141" s="49"/>
       <c r="L141" s="27"/>
       <c r="M141" s="27"/>
       <c r="N141" s="27"/>
@@ -16614,7 +16654,7 @@
       <c r="U141" s="27"/>
     </row>
     <row r="142" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K142" s="54"/>
+      <c r="K142" s="49"/>
       <c r="L142" s="27"/>
       <c r="M142" s="27"/>
       <c r="N142" s="27"/>
@@ -16627,7 +16667,7 @@
       <c r="U142" s="27"/>
     </row>
     <row r="143" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K143" s="54"/>
+      <c r="K143" s="49"/>
       <c r="L143" s="27"/>
       <c r="M143" s="27"/>
       <c r="N143" s="27"/>
@@ -16640,7 +16680,7 @@
       <c r="U143" s="27"/>
     </row>
     <row r="144" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K144" s="54"/>
+      <c r="K144" s="49"/>
       <c r="L144" s="27"/>
       <c r="M144" s="27"/>
       <c r="N144" s="27"/>
@@ -16653,7 +16693,7 @@
       <c r="U144" s="27"/>
     </row>
     <row r="145" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K145" s="54"/>
+      <c r="K145" s="49"/>
       <c r="L145" s="27"/>
       <c r="M145" s="27"/>
       <c r="N145" s="27"/>
@@ -16666,7 +16706,7 @@
       <c r="U145" s="27"/>
     </row>
     <row r="146" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K146" s="54"/>
+      <c r="K146" s="49"/>
       <c r="L146" s="27"/>
       <c r="M146" s="27"/>
       <c r="N146" s="27"/>
@@ -16679,7 +16719,7 @@
       <c r="U146" s="27"/>
     </row>
     <row r="147" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K147" s="54"/>
+      <c r="K147" s="49"/>
       <c r="L147" s="27"/>
       <c r="M147" s="27"/>
       <c r="N147" s="27"/>
@@ -16692,7 +16732,7 @@
       <c r="U147" s="27"/>
     </row>
     <row r="148" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K148" s="54"/>
+      <c r="K148" s="49"/>
       <c r="L148" s="27"/>
       <c r="M148" s="27"/>
       <c r="N148" s="27"/>
@@ -16705,7 +16745,7 @@
       <c r="U148" s="27"/>
     </row>
     <row r="149" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K149" s="54"/>
+      <c r="K149" s="49"/>
       <c r="L149" s="27"/>
       <c r="M149" s="27"/>
       <c r="N149" s="27"/>
@@ -16718,7 +16758,7 @@
       <c r="U149" s="27"/>
     </row>
     <row r="150" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K150" s="54"/>
+      <c r="K150" s="49"/>
       <c r="L150" s="27"/>
       <c r="M150" s="27"/>
       <c r="N150" s="27"/>
@@ -16731,7 +16771,7 @@
       <c r="U150" s="27"/>
     </row>
     <row r="151" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K151" s="54"/>
+      <c r="K151" s="49"/>
       <c r="L151" s="27"/>
       <c r="M151" s="27"/>
       <c r="N151" s="27"/>
@@ -16744,7 +16784,7 @@
       <c r="U151" s="27"/>
     </row>
     <row r="152" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K152" s="54"/>
+      <c r="K152" s="49"/>
       <c r="L152" s="27"/>
       <c r="M152" s="27"/>
       <c r="N152" s="27"/>
@@ -16757,7 +16797,7 @@
       <c r="U152" s="27"/>
     </row>
     <row r="153" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K153" s="54"/>
+      <c r="K153" s="49"/>
       <c r="L153" s="27"/>
       <c r="M153" s="27"/>
       <c r="N153" s="27"/>
@@ -16770,7 +16810,7 @@
       <c r="U153" s="27"/>
     </row>
     <row r="154" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K154" s="54"/>
+      <c r="K154" s="49"/>
       <c r="L154" s="27"/>
       <c r="M154" s="27"/>
       <c r="N154" s="27"/>
@@ -16783,7 +16823,7 @@
       <c r="U154" s="27"/>
     </row>
     <row r="155" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K155" s="54"/>
+      <c r="K155" s="49"/>
       <c r="L155" s="27"/>
       <c r="M155" s="27"/>
       <c r="N155" s="27"/>
@@ -16796,7 +16836,7 @@
       <c r="U155" s="27"/>
     </row>
     <row r="156" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K156" s="54"/>
+      <c r="K156" s="49"/>
       <c r="L156" s="27"/>
       <c r="M156" s="27"/>
       <c r="N156" s="27"/>
@@ -16809,7 +16849,7 @@
       <c r="U156" s="27"/>
     </row>
     <row r="157" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K157" s="54"/>
+      <c r="K157" s="49"/>
       <c r="L157" s="27"/>
       <c r="M157" s="27"/>
       <c r="N157" s="27"/>
@@ -16822,7 +16862,7 @@
       <c r="U157" s="27"/>
     </row>
     <row r="158" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K158" s="54"/>
+      <c r="K158" s="49"/>
       <c r="L158" s="27"/>
       <c r="M158" s="27"/>
       <c r="N158" s="27"/>
@@ -16835,7 +16875,7 @@
       <c r="U158" s="27"/>
     </row>
     <row r="159" spans="11:21" x14ac:dyDescent="0.25">
-      <c r="K159" s="54"/>
+      <c r="K159" s="49"/>
       <c r="L159" s="27"/>
       <c r="M159" s="27"/>
       <c r="N159" s="27"/>

--- a/Workpiece for tool.xlsx
+++ b/Workpiece for tool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atsus\bin\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87664B9C-A23F-4362-9567-84C79F81E9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A91E88-5850-48C6-A295-B242033511A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="1335" windowWidth="25350" windowHeight="15015" xr2:uid="{B1CDC31F-9E0C-410F-B3F2-978CA58E71C8}"/>
+    <workbookView xWindow="3180" yWindow="1335" windowWidth="23385" windowHeight="15015" activeTab="3" xr2:uid="{B1CDC31F-9E0C-410F-B3F2-978CA58E71C8}"/>
   </bookViews>
   <sheets>
     <sheet name="public" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="67">
   <si>
     <t>Use at your own risk.</t>
     <phoneticPr fontId="1"/>
@@ -2717,7 +2717,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3020,6 +3020,9 @@
     <xf numFmtId="0" fontId="64" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="OneNote_Dark" xfId="2" xr:uid="{9F542756-AF56-4026-83A6-A74E84FD4A3B}"/>
@@ -3030,16 +3033,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF201F1E"/>
+      <color rgb="FF0D1117"/>
       <color rgb="FFFFC000"/>
       <color rgb="FFFF9933"/>
       <color rgb="FF0066FF"/>
       <color rgb="FFCCFFFF"/>
-      <color rgb="FF0D1117"/>
       <color rgb="FFCC00FF"/>
       <color rgb="FFFF00FF"/>
       <color rgb="FFFFFFFF"/>
       <color rgb="FFFF9900"/>
-      <color rgb="FF00FFFF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -14730,7 +14733,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1540268B-B206-4F4D-8979-E712B9521EA3}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="B2:U159"/>
+  <dimension ref="B2:AA159"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2.33203125" style="4" customWidth="1"/>
@@ -14743,13 +14746,13 @@
     <col min="15" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:27" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" s="86" t="str" cm="1">
         <f t="array" aca="1" ref="B2" ca="1">RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1)))</f>
         <v>parts</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:27" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B3" s="85"/>
       <c r="C3" s="48" t="s">
         <v>42</v>
@@ -14768,7 +14771,7 @@
       <c r="T3" s="27"/>
       <c r="U3" s="27"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
       <c r="C4" s="13"/>
       <c r="J4" s="8"/>
       <c r="K4" s="50"/>
@@ -14783,7 +14786,7 @@
       <c r="T4" s="27"/>
       <c r="U4" s="27"/>
     </row>
-    <row r="5" spans="2:21" s="87" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:27" s="87" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="88"/>
       <c r="E5" s="92" t="s">
         <v>43</v>
@@ -14803,7 +14806,7 @@
       <c r="T5" s="91"/>
       <c r="U5" s="91"/>
     </row>
-    <row r="6" spans="2:21" ht="24" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:27" ht="24" x14ac:dyDescent="0.25">
       <c r="C6" s="88"/>
       <c r="E6" s="92" t="s">
         <v>43</v>
@@ -14823,7 +14826,7 @@
       <c r="T6" s="27"/>
       <c r="U6" s="27"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="J7" s="8"/>
       <c r="K7" s="50"/>
       <c r="L7" s="28"/>
@@ -14837,7 +14840,7 @@
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:27" x14ac:dyDescent="0.25">
       <c r="J8" s="8"/>
       <c r="K8" s="50"/>
       <c r="L8" s="28"/>
@@ -14851,7 +14854,7 @@
       <c r="T8" s="27"/>
       <c r="U8" s="27"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="K9" s="49"/>
       <c r="L9" s="27"/>
       <c r="M9" s="27"/>
@@ -14864,7 +14867,7 @@
       <c r="T9" s="27"/>
       <c r="U9" s="27"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="J10" s="8"/>
       <c r="K10" s="50"/>
       <c r="L10" s="28"/>
@@ -14878,7 +14881,7 @@
       <c r="T10" s="27"/>
       <c r="U10" s="27"/>
     </row>
-    <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J11" s="8"/>
       <c r="K11" s="50"/>
       <c r="L11" s="28"/>
@@ -14892,7 +14895,7 @@
       <c r="T11" s="27"/>
       <c r="U11" s="27"/>
     </row>
-    <row r="12" spans="2:21" s="96" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" s="96" customFormat="1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="C12" s="99" t="s">
         <v>48</v>
       </c>
@@ -14910,7 +14913,7 @@
       <c r="T12" s="98"/>
       <c r="U12" s="98"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="K13" s="49"/>
       <c r="L13" s="27"/>
       <c r="M13" s="27"/>
@@ -14923,7 +14926,7 @@
       <c r="T13" s="27"/>
       <c r="U13" s="27"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="K14" s="49"/>
       <c r="L14" s="27"/>
       <c r="M14" s="27"/>
@@ -14935,8 +14938,12 @@
       <c r="S14" s="27"/>
       <c r="T14" s="27"/>
       <c r="U14" s="27"/>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+    </row>
+    <row r="15" spans="2:27" ht="19.5" x14ac:dyDescent="0.25">
       <c r="K15" s="49"/>
       <c r="L15" s="27"/>
       <c r="M15" s="27"/>
@@ -14948,8 +14955,14 @@
       <c r="S15" s="27"/>
       <c r="T15" s="27"/>
       <c r="U15" s="27"/>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="X15" s="106" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+    </row>
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="D16" s="48" t="s">
         <v>59</v>
       </c>
@@ -14973,6 +14986,10 @@
       <c r="S16" s="27"/>
       <c r="T16" s="27"/>
       <c r="U16" s="27"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="4:21" x14ac:dyDescent="0.25">
       <c r="D17" s="48" t="s">

--- a/Workpiece for tool.xlsx
+++ b/Workpiece for tool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atsus\bin\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A91E88-5850-48C6-A295-B242033511A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417EA75B-3E4C-402C-830C-087A8B8A5BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1335" windowWidth="23385" windowHeight="15015" activeTab="3" xr2:uid="{B1CDC31F-9E0C-410F-B3F2-978CA58E71C8}"/>
+    <workbookView xWindow="3510" yWindow="645" windowWidth="22485" windowHeight="15180" xr2:uid="{B1CDC31F-9E0C-410F-B3F2-978CA58E71C8}"/>
   </bookViews>
   <sheets>
     <sheet name="public" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t>Use at your own risk.</t>
     <phoneticPr fontId="1"/>
@@ -1980,12 +1980,28 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>Excelにはマクロが含まれています。実行する場合は　　　　　　　　　　　　　　　　からセキュリティを許可してください。</t>
+    <rPh sb="11" eb="12">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>キョカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="66" x14ac:knownFonts="1">
+  <fonts count="67" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2498,6 +2514,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2717,7 +2740,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3021,6 +3044,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5492,6 +5518,182 @@
         <a:xfrm>
           <a:off x="6230439" y="3684077"/>
           <a:ext cx="346088" cy="361627"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>52085</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>170446</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>671150</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3263</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0352D876-4CA9-ACCE-0232-3E720C7AA741}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2728378" y="9960287"/>
+          <a:ext cx="619065" cy="232403"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>643638</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>150394</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>308106</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>45118</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{331ACC4A-2F2F-AF14-D716-439645D2BC00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3319931" y="9940235"/>
+          <a:ext cx="426468" cy="294310"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>646698</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>145381</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>56278</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>49172</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="図 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8D384DD-7615-8B6B-755B-3CBAEFF6AE36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8868277" y="9941092"/>
+          <a:ext cx="933580" cy="304843"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>711869</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>145381</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>483343</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>30119</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="図 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEBA2868-937C-A0A6-FF5D-200092BC6315}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9695448" y="9941092"/>
+          <a:ext cx="533474" cy="285790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10727,7 +10929,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B6A63E-25D5-4BD7-93A4-A70981612B63}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:S77"/>
+  <dimension ref="B2:T77"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
@@ -11341,7 +11543,7 @@
       <c r="R32" s="27"/>
       <c r="S32" s="2"/>
     </row>
-    <row r="33" spans="3:19" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:20" ht="52.5" x14ac:dyDescent="0.25">
       <c r="C33" s="21" t="s">
         <v>26</v>
       </c>
@@ -11363,7 +11565,7 @@
       <c r="R33" s="27"/>
       <c r="S33" s="2"/>
     </row>
-    <row r="34" spans="3:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C34" s="8" t="s">
         <v>29</v>
       </c>
@@ -11385,7 +11587,7 @@
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
     </row>
-    <row r="35" spans="3:19" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:20" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -11402,7 +11604,7 @@
       <c r="Q35" s="27"/>
       <c r="R35" s="27"/>
     </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -11420,7 +11622,7 @@
       <c r="R36" s="10"/>
       <c r="S36" s="2"/>
     </row>
-    <row r="37" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C37" s="13"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -11438,7 +11640,7 @@
       <c r="R37" s="10"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
@@ -11456,7 +11658,7 @@
       <c r="R38" s="10"/>
       <c r="S38" s="2"/>
     </row>
-    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="13"/>
@@ -11473,7 +11675,7 @@
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
     </row>
-    <row r="40" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
@@ -11489,16 +11691,22 @@
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
-    </row>
-    <row r="41" spans="3:19" x14ac:dyDescent="0.25">
-      <c r="C41" s="4"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+    </row>
+    <row r="41" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C41" s="107" t="s">
+        <v>67</v>
+      </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="K41" s="10"/>
+      <c r="K41" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -11506,8 +11714,10 @@
       <c r="P41" s="10"/>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
-    </row>
-    <row r="42" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+    </row>
+    <row r="42" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -11523,8 +11733,10 @@
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
-    </row>
-    <row r="43" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
+    </row>
+    <row r="43" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -11540,8 +11752,10 @@
       <c r="P43" s="10"/>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
-    </row>
-    <row r="44" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+    </row>
+    <row r="44" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -11558,7 +11772,7 @@
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
     </row>
-    <row r="45" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -11575,7 +11789,7 @@
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
     </row>
-    <row r="46" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -11592,7 +11806,7 @@
       <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
     </row>
-    <row r="47" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -11609,7 +11823,7 @@
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
     </row>
-    <row r="48" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>

--- a/Workpiece for tool.xlsx
+++ b/Workpiece for tool.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atsus\bin\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417EA75B-3E4C-402C-830C-087A8B8A5BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAD0EBD-E90B-4907-B260-7B38573CB589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="645" windowWidth="22485" windowHeight="15180" xr2:uid="{B1CDC31F-9E0C-410F-B3F2-978CA58E71C8}"/>
+    <workbookView xWindow="930" yWindow="810" windowWidth="26160" windowHeight="14220" activeTab="4" xr2:uid="{B1CDC31F-9E0C-410F-B3F2-978CA58E71C8}"/>
   </bookViews>
   <sheets>
     <sheet name="public" sheetId="1" r:id="rId1"/>
     <sheet name="repos" sheetId="4" r:id="rId2"/>
     <sheet name="Portfolio" sheetId="2" r:id="rId3"/>
-    <sheet name="parts" sheetId="5" r:id="rId4"/>
+    <sheet name="SDGuide" sheetId="6" r:id="rId4"/>
+    <sheet name="parts" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="83">
   <si>
     <t>Use at your own risk.</t>
     <phoneticPr fontId="1"/>
@@ -1996,12 +1997,197 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>SoftwareDevelopmentGuide</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　要件定義</t>
+    <rPh sb="1" eb="3">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　基本設計</t>
+    <rPh sb="1" eb="3">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　詳細設計 (コーディング規約)</t>
+    <rPh sb="1" eb="3">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　UI設計</t>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　Git運用</t>
+    <rPh sb="4" eb="6">
+      <t>ウンヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　開発環境毎のテンプレート</t>
+    <rPh sb="1" eb="3">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゴト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　Docker構築</t>
+    <rPh sb="7" eb="9">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　リリース手順</t>
+    <rPh sb="5" eb="7">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ドキュメント作成</t>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　Development Checklist</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="36"/>
+        <color rgb="FF66FFFF"/>
+        <rFont val="Segoe UI Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>tmct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FFFF66FF"/>
+        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>[Tkinter]</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　・リハビリでの使用を想定したカウントダウンタイマー と タイマー実行数カウンタです。</t>
+    <rPh sb="8" eb="10">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　・一定時間の姿勢維持を数セット行う等のリハビリテーションを支援します。</t>
+    <rPh sb="2" eb="4">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ナド</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="36"/>
+        <color rgb="FF0066FF"/>
+        <rFont val="Segoe UI Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>tmct</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FFCC00FF"/>
+        <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>[Tkinter]</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="67" x14ac:knownFonts="1">
+  <fonts count="71" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2521,6 +2707,40 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="22"/>
+      <color rgb="FF66FFFF"/>
+      <name val="HG丸ｺﾞｼｯｸM-PRO"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="22"/>
+      <color rgb="FF0066FF"/>
+      <name val="HG丸ｺﾞｼｯｸM-PRO"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0066FF"/>
+      <name val="HG丸ｺﾞｼｯｸM-PRO"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="18"/>
+      <color rgb="FFFF99FF"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2560,7 +2780,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -2728,6 +2948,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2740,7 +3043,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3049,6 +3352,48 @@
     <xf numFmtId="0" fontId="66" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="OneNote_Dark" xfId="2" xr:uid="{9F542756-AF56-4026-83A6-A74E84FD4A3B}"/>
@@ -3059,16 +3404,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCC00FF"/>
+      <color rgb="FFFF66FF"/>
+      <color rgb="FF0000FF"/>
+      <color rgb="FF0066FF"/>
+      <color rgb="FFCCFFFF"/>
       <color rgb="FF201F1E"/>
       <color rgb="FF0D1117"/>
       <color rgb="FFFFC000"/>
       <color rgb="FFFF9933"/>
-      <color rgb="FF0066FF"/>
-      <color rgb="FFCCFFFF"/>
-      <color rgb="FFCC00FF"/>
       <color rgb="FFFF00FF"/>
-      <color rgb="FFFFFFFF"/>
-      <color rgb="FFFF9900"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3084,6 +3429,94 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>92528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>473528</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>451756</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="図 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54C29C2B-D7E2-6FA8-9818-FE31BD3ABA94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6242957" y="9307285"/>
+          <a:ext cx="359228" cy="359228"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>92528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>473528</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>451756</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="図 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6997A7A7-27ED-C284-4D97-2F4A605CAB63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="696686" y="9307285"/>
+          <a:ext cx="359228" cy="359228"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -3111,7 +3544,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3150,7 +3583,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3189,7 +3622,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3717,7 +4150,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3978,7 +4411,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4231,7 +4664,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4504,7 +4937,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4881,7 +5314,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4920,7 +5353,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4959,7 +5392,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4998,7 +5431,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5037,7 +5470,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5289,7 +5722,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5333,7 +5766,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5377,7 +5810,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5421,7 +5854,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5465,7 +5898,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5509,7 +5942,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5530,14 +5963,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>52085</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>170446</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>671150</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>3263</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>3264</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5553,7 +5986,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5574,14 +6007,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>643638</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>150394</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>308106</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>45118</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>45119</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5597,7 +6030,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5618,14 +6051,14 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>646698</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>145381</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>56278</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>49172</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>49173</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5641,7 +6074,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5662,14 +6095,14 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>711869</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>145381</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>483343</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>30119</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>30120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5685,7 +6118,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5702,6 +6135,389 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>470448</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>217114</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="258903" cy="259566"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E37CE30-0D51-4431-8A9D-46EBB31B94E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3148334" y="5300743"/>
+          <a:ext cx="258903" cy="259566"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7453FDB-BE85-4BCC-B229-97550888E5E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="582386" y="5083630"/>
+          <a:ext cx="4381500" cy="1377041"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>　</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>47157</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>179556</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1406091" cy="211725"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F61EAF7-55CE-4D47-95B6-B66A527499C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1201043" y="9192927"/>
+          <a:ext cx="1406091" cy="211725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000" b="0" i="1">
+              <a:solidFill>
+                <a:srgbClr val="FF66FF"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>Clock Timer &amp; Counter</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="0" i="1">
+            <a:solidFill>
+              <a:srgbClr val="FF66FF"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>47157</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>151658</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1275606" cy="232884"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="テキスト ボックス 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49082256-2FAD-4AC7-B1D1-AA4652C7B24C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6747314" y="9165029"/>
+          <a:ext cx="1275606" cy="232884"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" i="1">
+              <a:solidFill>
+                <a:srgbClr val="CC00FF"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Clock Timer &amp; Counter</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000" b="0" i="1">
+            <a:solidFill>
+              <a:srgbClr val="CC00FF"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>194423</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>99172</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04E3CA5F-B640-4488-BBA1-2A7E5B67048B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6128657" y="5076666"/>
+          <a:ext cx="4381500" cy="1281792"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>　</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>473488</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>217114</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="258903" cy="259566"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="図 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8163E441-A0DD-40AD-98B1-69DB7A7EE359}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8697645" y="5300743"/>
+          <a:ext cx="258903" cy="259566"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9858,6 +10674,2463 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104539</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>61785</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="569128" cy="573593"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E587834C-AA57-42EF-8777-AD26CB945BEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="503974" y="968196"/>
+          <a:ext cx="569128" cy="573593"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>122975</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>61785</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="569128" cy="573593"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BBBCCFB-BCA8-4FC3-B581-BB0F96EB3D82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7217564" y="968196"/>
+          <a:ext cx="569128" cy="573593"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>187324</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>193675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>26276</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4357ED3-8A00-4A72-87A6-5B0F68A6EB6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6881100" y="889985"/>
+          <a:ext cx="5179521" cy="998045"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>200026</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19708</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{192B2CA6-3A42-4312-8AD4-35BADF38A350}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="387568" y="896336"/>
+          <a:ext cx="5169778" cy="994870"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="993413" cy="515782"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="テキスト ボックス 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F55C436E-5F93-44F0-9510-CB22F89CF2C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1251388" y="1173217"/>
+          <a:ext cx="993413" cy="515782"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1" i="1">
+              <a:solidFill>
+                <a:srgbClr val="CC00FF"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>public</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000" b="1" i="1">
+            <a:solidFill>
+              <a:srgbClr val="CC00FF"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="993413" cy="515782"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F26DB7E-D931-4E88-8DF8-23833696E453}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7748095" y="1173217"/>
+          <a:ext cx="993413" cy="515782"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000" b="1" i="1">
+              <a:solidFill>
+                <a:srgbClr val="CC00FF"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>public</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000" b="1" i="1">
+            <a:solidFill>
+              <a:srgbClr val="CC00FF"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78A36D72-CE69-434E-88D0-FFF6CCE3B574}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="451738" y="2112577"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="図 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7C84D8D-51E3-4598-B6B0-090CFA1F5533}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="451738" y="2112577"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>185650</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>195983</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4368</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>17626</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="正方形/長方形 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5401BD9F-049C-767C-F962-1447BDB0CE16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="385368" y="1999588"/>
+          <a:ext cx="2304435" cy="460740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="図 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEEDB6B3-B9ED-4240-935A-AB9F406FA7AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="447957" y="2114941"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="図 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{546E1E45-1FFC-4C8C-A7A5-CF1CF895FBE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2733957" y="2114941"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>190396</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>201761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="87" name="正方形/長方形 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C81E42F2-E05A-CED1-54BA-0DC3728F1EB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7085267" y="2005366"/>
+          <a:ext cx="2295322" cy="452699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1141</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>195983</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19576</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>17626</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="89" name="正方形/長方形 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A367EF9-0BB5-E21F-5D61-A388B27BC4B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2687514" y="2000890"/>
+          <a:ext cx="2304435" cy="460948"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>761896</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>201761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>9218</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="90" name="正方形/長方形 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A6C18B7-8BEB-D88F-8B83-602E000DB915}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9380485" y="2005366"/>
+          <a:ext cx="2295322" cy="452699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="図 98">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5E27D0B-C8E4-4E05-AEE7-C38B1B32206C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="451888" y="2102610"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>185650</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>203415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>13940</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>17626</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="101" name="正方形/長方形 100">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BD06F1A-13F8-4B63-98AA-A4609E44ECAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="385836" y="2647627"/>
+          <a:ext cx="4600477" cy="463202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="図 101">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5511819-3110-4933-B13E-7C1C6D00C46B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7147266" y="2102610"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="図 106">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0208EF2-B065-4AD4-8FAA-D96D89BF83F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="451888" y="2102610"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="図 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9299227-0B52-4124-B80A-4B09C17992F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2737888" y="2102610"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>185650</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>206644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4368</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="109" name="正方形/長方形 108">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DB3F126-52CD-4537-A150-50E5FFBEB07F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="385836" y="3299847"/>
+          <a:ext cx="2304905" cy="461508"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="図 109">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A308A8B9-8903-4C6D-8EAD-7F9AADA93A30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7147266" y="2102610"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="図 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E15E1CB7-B627-4DBB-973B-2EECBC12BC47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9433266" y="2102610"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>190396</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>209873</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="112" name="正方形/長方形 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B552276-CEFD-46D8-93D8-85477C183F77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7087142" y="3303076"/>
+          <a:ext cx="2295790" cy="454482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4371</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>206644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>14289</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="113" name="正方形/長方形 112">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3AE03E5-42E6-4F8F-B321-4B6C2F8E00FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2690744" y="3299847"/>
+          <a:ext cx="2295918" cy="461508"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>761896</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>209873</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>9218</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="114" name="正方形/長方形 113">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E987246B-4584-4CBF-88B6-B40024C04F88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9382828" y="3303076"/>
+          <a:ext cx="2295322" cy="454482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>185750</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>211053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>13940</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="147" name="正方形/長方形 146">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD9179C4-C397-475F-9FD8-293DDB21AAB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7080921" y="2641090"/>
+          <a:ext cx="4599982" cy="450151"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="148" name="図 147">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{408C692E-F83E-4CAD-BF29-C6681A977C50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="452353" y="2757512"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>185650</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>203415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>13940</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>17626</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="149" name="正方形/長方形 148">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B090F3AD-E709-41AD-93DD-DCD07469D22A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="385836" y="3945610"/>
+          <a:ext cx="4600477" cy="463202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="150" name="図 149">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{921ED11B-5EF9-4809-9E70-C0D84601B7A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7148428" y="2757512"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>185750</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>211053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>13940</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="151" name="正方形/長方形 150">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCC264DF-0DC6-414F-89A3-7DF8ACF9EE99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7081850" y="2649453"/>
+          <a:ext cx="4600215" cy="452010"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="152" name="図 151">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EDFBDFD-0BF4-4231-9F81-510BA7E40A66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="452353" y="3405212"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="153" name="図 152">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D941A88F-4451-45F4-93A3-5672DB84E0A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2738353" y="3405212"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>185650</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>203416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4368</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="154" name="正方形/長方形 153">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51EEA2BE-7F50-48E5-BB8D-409079A8A4FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="385836" y="4594602"/>
+          <a:ext cx="2304905" cy="464736"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="155" name="図 154">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36773D98-7149-4972-A3BF-25AF45D7BA88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7148428" y="3405212"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="156" name="図 155">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{110309EC-E157-402C-A967-3DF91F3823D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9434428" y="3405212"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>190396</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>209873</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="157" name="正方形/長方形 156">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{063FF142-4CF6-4BB4-92C0-20C52735C5A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7087142" y="4601059"/>
+          <a:ext cx="2295790" cy="454482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4371</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>203416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>14289</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="158" name="正方形/長方形 157">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81C18561-B019-4025-8813-1194C663814F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2690744" y="4594602"/>
+          <a:ext cx="2295918" cy="464736"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>761896</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>209873</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>9218</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="159" name="正方形/長方形 158">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BECC303-65D2-4BB5-AC6A-BC6B9F8CB6FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9382828" y="4601059"/>
+          <a:ext cx="2295322" cy="454482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="160" name="図 159">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06E04CAE-1D33-4FA2-BC8D-EB06D6FE9DFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="452353" y="4052912"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>185650</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>203415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>13940</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>17626</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="161" name="正方形/長方形 160">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8B1471A-22F5-4DF3-B810-4F5762B79B09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="385675" y="5232615"/>
+          <a:ext cx="4600315" cy="461911"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="162" name="図 161">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{309F91E9-F96F-4EEA-8CEA-D2027AC42B62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7148428" y="4052912"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>185750</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>211053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>13940</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="163" name="正方形/長方形 162">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20AEE796-17BC-4901-B0FC-8C200A2091E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7081850" y="3944853"/>
+          <a:ext cx="4600215" cy="452010"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6F7F2A3-EFDE-480B-8EA3-E3B5A4797F83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="452353" y="5348312"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>185650</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>203415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>13940</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>17626</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E05BCFDE-199B-4D27-977E-9826E73095E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="385675" y="5232615"/>
+          <a:ext cx="4600315" cy="461911"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>52303</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="290971" cy="293254"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53DA9F1D-69C4-4539-8C99-C4A49A7EC841}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7148428" y="5348312"/>
+          <a:ext cx="290971" cy="293254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>185750</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>211053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>13940</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>15363</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EE2DC59-E09B-4560-A425-9CE39AAF6555}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7081850" y="5240253"/>
+          <a:ext cx="4600215" cy="452010"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>585079</xdr:colOff>
       <xdr:row>4</xdr:row>
@@ -10628,6 +13901,206 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>608400</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>160725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="四角形: 角を丸くする 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48A2DFCC-DD7A-34FB-BC58-B4FD8EF83176}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3714750" y="5257800"/>
+          <a:ext cx="2437200" cy="2437200"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="CCFFFF"/>
+        </a:solidFill>
+        <a:ln w="79375">
+          <a:solidFill>
+            <a:srgbClr val="0066FF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28CE2EEA-AA7D-B3F7-3F99-A5A2B3A6F267}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3876675" y="5419725"/>
+          <a:ext cx="2152650" cy="2152650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>235719</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>86879</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1062086" cy="1408548"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80C2F1F9-1839-0345-62F6-45EB7EC02824}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3320038" y="5994160"/>
+          <a:ext cx="1408548" cy="1062086"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="4400" b="1">
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:shade val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans JP Black" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Noto Sans JP Black" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>tmct</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="4400" b="1">
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="0000FF"/>
+            </a:solidFill>
+            <a:latin typeface="Noto Sans JP Black" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Noto Sans JP Black" panose="020B0200000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10929,7 +14402,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B6A63E-25D5-4BD7-93A4-A70981612B63}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:T77"/>
+  <dimension ref="B2:T80"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
@@ -11622,17 +15095,21 @@
       <c r="R36" s="10"/>
       <c r="S36" s="2"/>
     </row>
-    <row r="37" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C37" s="13"/>
-      <c r="D37" s="4"/>
+    <row r="37" spans="3:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="4"/>
+      <c r="D37" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="K37" s="27"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="121" t="s">
+        <v>82</v>
+      </c>
       <c r="N37" s="10"/>
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
@@ -11640,73 +15117,79 @@
       <c r="R37" s="10"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
+    <row r="38" spans="3:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="27"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="2"/>
-    </row>
-    <row r="39" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-    </row>
-    <row r="40" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
+      <c r="L38" s="29" t="str">
+        <f>C38</f>
+        <v>　・リハビリでの使用を想定したカウントダウンタイマー と タイマー実行数カウンタです。</v>
+      </c>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11"/>
+    </row>
+    <row r="39" spans="3:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="29" t="str">
+        <f>C39</f>
+        <v>　・一定時間の姿勢維持を数セット行う等のリハビリテーションを支援します。</v>
+      </c>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+    </row>
+    <row r="40" spans="3:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
     </row>
     <row r="41" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C41" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="K41" s="10" t="s">
-        <v>67</v>
-      </c>
+      <c r="K41" s="27"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -11714,14 +15197,13 @@
       <c r="P41" s="10"/>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
+      <c r="S41" s="2"/>
     </row>
     <row r="42" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -11733,14 +15215,12 @@
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
-      <c r="S42" s="10"/>
-      <c r="T42" s="10"/>
     </row>
     <row r="43" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -11756,14 +15236,18 @@
       <c r="T43" s="10"/>
     </row>
     <row r="44" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C44" s="4"/>
+      <c r="C44" s="107" t="s">
+        <v>67</v>
+      </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="K44" s="10"/>
+      <c r="K44" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
       <c r="N44" s="10"/>
@@ -11771,6 +15255,8 @@
       <c r="P44" s="10"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
     </row>
     <row r="45" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C45" s="4"/>
@@ -11788,6 +15274,8 @@
       <c r="P45" s="10"/>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
     </row>
     <row r="46" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C46" s="4"/>
@@ -11805,6 +15293,8 @@
       <c r="P46" s="10"/>
       <c r="Q46" s="10"/>
       <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
     </row>
     <row r="47" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C47" s="4"/>
@@ -12317,6 +15807,13 @@
       <c r="R76" s="10"/>
     </row>
     <row r="77" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>
       <c r="M77" s="10"/>
@@ -12325,6 +15822,50 @@
       <c r="P77" s="10"/>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
+    </row>
+    <row r="78" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="K78" s="10"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="10"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
+    </row>
+    <row r="79" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="K79" s="10"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="10"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+    </row>
+    <row r="80" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="K80" s="10"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="10"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -14945,6 +18486,2191 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC67326C-FDD4-4397-8182-0C417E8CDE8F}">
+  <dimension ref="B2:U158"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="2.33203125" style="4" customWidth="1"/>
+    <col min="3" max="9" width="8.88671875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="4"/>
+    <col min="11" max="13" width="2.33203125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:21" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="85" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="85"/>
+      <c r="C3" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="49"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+    </row>
+    <row r="4" spans="2:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="13"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+    </row>
+    <row r="5" spans="2:21" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="51"/>
+      <c r="D5" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="27"/>
+    </row>
+    <row r="6" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="55"/>
+      <c r="D6" s="56"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="27"/>
+    </row>
+    <row r="7" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+    </row>
+    <row r="8" spans="2:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="49"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+    </row>
+    <row r="9" spans="2:21" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="108" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="109"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="108" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="109"/>
+      <c r="H9" s="110"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="O9" s="112"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="R9" s="112"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="114"/>
+      <c r="U9" s="27"/>
+    </row>
+    <row r="10" spans="2:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="49"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+    </row>
+    <row r="11" spans="2:21" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="115" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="117"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" s="119"/>
+      <c r="P11" s="119"/>
+      <c r="Q11" s="119"/>
+      <c r="R11" s="119"/>
+      <c r="S11" s="120"/>
+      <c r="T11" s="114"/>
+      <c r="U11" s="27"/>
+    </row>
+    <row r="12" spans="2:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="49"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+    </row>
+    <row r="13" spans="2:21" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="108" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="109"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="109"/>
+      <c r="H13" s="110"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="111" t="s">
+        <v>72</v>
+      </c>
+      <c r="O13" s="112"/>
+      <c r="P13" s="113"/>
+      <c r="Q13" s="111" t="s">
+        <v>73</v>
+      </c>
+      <c r="R13" s="112"/>
+      <c r="S13" s="113"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="27"/>
+    </row>
+    <row r="14" spans="2:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="49"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+    </row>
+    <row r="15" spans="2:21" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="115" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="117"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="118" t="s">
+        <v>74</v>
+      </c>
+      <c r="O15" s="119"/>
+      <c r="P15" s="119"/>
+      <c r="Q15" s="119"/>
+      <c r="R15" s="119"/>
+      <c r="S15" s="120"/>
+      <c r="T15" s="114"/>
+      <c r="U15" s="27"/>
+    </row>
+    <row r="16" spans="2:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="49"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+    </row>
+    <row r="17" spans="3:21" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="108" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="109"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="109" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="109"/>
+      <c r="H17" s="110"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="50"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="111" t="s">
+        <v>75</v>
+      </c>
+      <c r="O17" s="112"/>
+      <c r="P17" s="113"/>
+      <c r="Q17" s="111" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" s="112"/>
+      <c r="S17" s="113"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="27"/>
+    </row>
+    <row r="18" spans="3:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="49"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+    </row>
+    <row r="19" spans="3:21" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="115" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="117"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="118" t="s">
+        <v>77</v>
+      </c>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="119"/>
+      <c r="R19" s="119"/>
+      <c r="S19" s="120"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="27"/>
+    </row>
+    <row r="20" spans="3:21" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="49"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+    </row>
+    <row r="21" spans="3:21" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="115" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="116"/>
+      <c r="H21" s="117"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="O21" s="119"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="119"/>
+      <c r="R21" s="119"/>
+      <c r="S21" s="120"/>
+      <c r="T21" s="114"/>
+      <c r="U21" s="27"/>
+    </row>
+    <row r="22" spans="3:21" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="K22" s="49"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K23" s="49"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K24" s="49"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K25" s="49"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K26" s="49"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K27" s="49"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+    </row>
+    <row r="28" spans="3:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="8"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K29" s="49"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K30" s="49"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K31" s="49"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="K32" s="49"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
+    </row>
+    <row r="33" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K33" s="49"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="27"/>
+    </row>
+    <row r="34" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K34" s="49"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
+      <c r="P34" s="27"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="27"/>
+    </row>
+    <row r="35" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K35" s="49"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="27"/>
+      <c r="P35" s="27"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="27"/>
+    </row>
+    <row r="36" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K36" s="49"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="27"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="27"/>
+    </row>
+    <row r="37" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K37" s="49"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
+    </row>
+    <row r="38" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K38" s="49"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
+      <c r="O38" s="27"/>
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="27"/>
+    </row>
+    <row r="39" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K39" s="49"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="27"/>
+      <c r="N39" s="27"/>
+      <c r="O39" s="27"/>
+      <c r="P39" s="27"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27"/>
+      <c r="T39" s="27"/>
+      <c r="U39" s="27"/>
+    </row>
+    <row r="40" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K40" s="49"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+    </row>
+    <row r="41" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K41" s="49"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="27"/>
+      <c r="P41" s="27"/>
+      <c r="Q41" s="27"/>
+      <c r="R41" s="27"/>
+      <c r="S41" s="27"/>
+      <c r="T41" s="27"/>
+      <c r="U41" s="27"/>
+    </row>
+    <row r="42" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K42" s="49"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="27"/>
+      <c r="P42" s="27"/>
+      <c r="Q42" s="27"/>
+      <c r="R42" s="27"/>
+      <c r="S42" s="27"/>
+      <c r="T42" s="27"/>
+      <c r="U42" s="27"/>
+    </row>
+    <row r="43" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K43" s="49"/>
+      <c r="L43" s="27"/>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="27"/>
+      <c r="P43" s="27"/>
+      <c r="Q43" s="27"/>
+      <c r="R43" s="27"/>
+      <c r="S43" s="27"/>
+      <c r="T43" s="27"/>
+      <c r="U43" s="27"/>
+    </row>
+    <row r="44" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K44" s="49"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="27"/>
+      <c r="Q44" s="27"/>
+      <c r="R44" s="27"/>
+      <c r="S44" s="27"/>
+      <c r="T44" s="27"/>
+      <c r="U44" s="27"/>
+    </row>
+    <row r="45" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K45" s="49"/>
+      <c r="L45" s="27"/>
+      <c r="M45" s="27"/>
+      <c r="N45" s="27"/>
+      <c r="O45" s="27"/>
+      <c r="P45" s="27"/>
+      <c r="Q45" s="27"/>
+      <c r="R45" s="27"/>
+      <c r="S45" s="27"/>
+      <c r="T45" s="27"/>
+      <c r="U45" s="27"/>
+    </row>
+    <row r="46" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K46" s="49"/>
+      <c r="L46" s="27"/>
+      <c r="M46" s="27"/>
+      <c r="N46" s="27"/>
+      <c r="O46" s="27"/>
+      <c r="P46" s="27"/>
+      <c r="Q46" s="27"/>
+      <c r="R46" s="27"/>
+      <c r="S46" s="27"/>
+      <c r="T46" s="27"/>
+      <c r="U46" s="27"/>
+    </row>
+    <row r="47" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K47" s="49"/>
+      <c r="L47" s="27"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="27"/>
+      <c r="P47" s="27"/>
+      <c r="Q47" s="27"/>
+      <c r="R47" s="27"/>
+      <c r="S47" s="27"/>
+      <c r="T47" s="27"/>
+      <c r="U47" s="27"/>
+    </row>
+    <row r="48" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K48" s="49"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="27"/>
+      <c r="R48" s="27"/>
+      <c r="S48" s="27"/>
+      <c r="T48" s="27"/>
+      <c r="U48" s="27"/>
+    </row>
+    <row r="49" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K49" s="49"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="27"/>
+      <c r="P49" s="27"/>
+      <c r="Q49" s="27"/>
+      <c r="R49" s="27"/>
+      <c r="S49" s="27"/>
+      <c r="T49" s="27"/>
+      <c r="U49" s="27"/>
+    </row>
+    <row r="50" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K50" s="49"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="27"/>
+      <c r="N50" s="27"/>
+      <c r="O50" s="27"/>
+      <c r="P50" s="27"/>
+      <c r="Q50" s="27"/>
+      <c r="R50" s="27"/>
+      <c r="S50" s="27"/>
+      <c r="T50" s="27"/>
+      <c r="U50" s="27"/>
+    </row>
+    <row r="51" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K51" s="49"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="27"/>
+      <c r="N51" s="27"/>
+      <c r="O51" s="27"/>
+      <c r="P51" s="27"/>
+      <c r="Q51" s="27"/>
+      <c r="R51" s="27"/>
+      <c r="S51" s="27"/>
+      <c r="T51" s="27"/>
+      <c r="U51" s="27"/>
+    </row>
+    <row r="52" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K52" s="49"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="27"/>
+      <c r="N52" s="27"/>
+      <c r="O52" s="27"/>
+      <c r="P52" s="27"/>
+      <c r="Q52" s="27"/>
+      <c r="R52" s="27"/>
+      <c r="S52" s="27"/>
+      <c r="T52" s="27"/>
+      <c r="U52" s="27"/>
+    </row>
+    <row r="53" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K53" s="49"/>
+      <c r="L53" s="27"/>
+      <c r="M53" s="27"/>
+      <c r="N53" s="27"/>
+      <c r="O53" s="27"/>
+      <c r="P53" s="27"/>
+      <c r="Q53" s="27"/>
+      <c r="R53" s="27"/>
+      <c r="S53" s="27"/>
+      <c r="T53" s="27"/>
+      <c r="U53" s="27"/>
+    </row>
+    <row r="54" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K54" s="49"/>
+      <c r="L54" s="27"/>
+      <c r="M54" s="27"/>
+      <c r="N54" s="27"/>
+      <c r="O54" s="27"/>
+      <c r="P54" s="27"/>
+      <c r="Q54" s="27"/>
+      <c r="R54" s="27"/>
+      <c r="S54" s="27"/>
+      <c r="T54" s="27"/>
+      <c r="U54" s="27"/>
+    </row>
+    <row r="55" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K55" s="49"/>
+      <c r="L55" s="27"/>
+      <c r="M55" s="27"/>
+      <c r="N55" s="27"/>
+      <c r="O55" s="27"/>
+      <c r="P55" s="27"/>
+      <c r="Q55" s="27"/>
+      <c r="R55" s="27"/>
+      <c r="S55" s="27"/>
+      <c r="T55" s="27"/>
+      <c r="U55" s="27"/>
+    </row>
+    <row r="56" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K56" s="49"/>
+      <c r="L56" s="27"/>
+      <c r="M56" s="27"/>
+      <c r="N56" s="27"/>
+      <c r="O56" s="27"/>
+      <c r="P56" s="27"/>
+      <c r="Q56" s="27"/>
+      <c r="R56" s="27"/>
+      <c r="S56" s="27"/>
+      <c r="T56" s="27"/>
+      <c r="U56" s="27"/>
+    </row>
+    <row r="57" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K57" s="49"/>
+      <c r="L57" s="27"/>
+      <c r="M57" s="27"/>
+      <c r="N57" s="27"/>
+      <c r="O57" s="27"/>
+      <c r="P57" s="27"/>
+      <c r="Q57" s="27"/>
+      <c r="R57" s="27"/>
+      <c r="S57" s="27"/>
+      <c r="T57" s="27"/>
+      <c r="U57" s="27"/>
+    </row>
+    <row r="58" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K58" s="49"/>
+      <c r="L58" s="27"/>
+      <c r="M58" s="27"/>
+      <c r="N58" s="27"/>
+      <c r="O58" s="27"/>
+      <c r="P58" s="27"/>
+      <c r="Q58" s="27"/>
+      <c r="R58" s="27"/>
+      <c r="S58" s="27"/>
+      <c r="T58" s="27"/>
+      <c r="U58" s="27"/>
+    </row>
+    <row r="59" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K59" s="49"/>
+      <c r="L59" s="27"/>
+      <c r="M59" s="27"/>
+      <c r="N59" s="27"/>
+      <c r="O59" s="27"/>
+      <c r="P59" s="27"/>
+      <c r="Q59" s="27"/>
+      <c r="R59" s="27"/>
+      <c r="S59" s="27"/>
+      <c r="T59" s="27"/>
+      <c r="U59" s="27"/>
+    </row>
+    <row r="60" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K60" s="49"/>
+      <c r="L60" s="27"/>
+      <c r="M60" s="27"/>
+      <c r="N60" s="27"/>
+      <c r="O60" s="27"/>
+      <c r="P60" s="27"/>
+      <c r="Q60" s="27"/>
+      <c r="R60" s="27"/>
+      <c r="S60" s="27"/>
+      <c r="T60" s="27"/>
+      <c r="U60" s="27"/>
+    </row>
+    <row r="61" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K61" s="49"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27"/>
+      <c r="P61" s="27"/>
+      <c r="Q61" s="27"/>
+      <c r="R61" s="27"/>
+      <c r="S61" s="27"/>
+      <c r="T61" s="27"/>
+      <c r="U61" s="27"/>
+    </row>
+    <row r="62" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K62" s="49"/>
+      <c r="L62" s="27"/>
+      <c r="M62" s="27"/>
+      <c r="N62" s="27"/>
+      <c r="O62" s="27"/>
+      <c r="P62" s="27"/>
+      <c r="Q62" s="27"/>
+      <c r="R62" s="27"/>
+      <c r="S62" s="27"/>
+      <c r="T62" s="27"/>
+      <c r="U62" s="27"/>
+    </row>
+    <row r="63" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K63" s="49"/>
+      <c r="L63" s="27"/>
+      <c r="M63" s="27"/>
+      <c r="N63" s="27"/>
+      <c r="O63" s="27"/>
+      <c r="P63" s="27"/>
+      <c r="Q63" s="27"/>
+      <c r="R63" s="27"/>
+      <c r="S63" s="27"/>
+      <c r="T63" s="27"/>
+      <c r="U63" s="27"/>
+    </row>
+    <row r="64" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K64" s="49"/>
+      <c r="L64" s="27"/>
+      <c r="M64" s="27"/>
+      <c r="N64" s="27"/>
+      <c r="O64" s="27"/>
+      <c r="P64" s="27"/>
+      <c r="Q64" s="27"/>
+      <c r="R64" s="27"/>
+      <c r="S64" s="27"/>
+      <c r="T64" s="27"/>
+      <c r="U64" s="27"/>
+    </row>
+    <row r="65" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K65" s="49"/>
+      <c r="L65" s="27"/>
+      <c r="M65" s="27"/>
+      <c r="N65" s="27"/>
+      <c r="O65" s="27"/>
+      <c r="P65" s="27"/>
+      <c r="Q65" s="27"/>
+      <c r="R65" s="27"/>
+      <c r="S65" s="27"/>
+      <c r="T65" s="27"/>
+      <c r="U65" s="27"/>
+    </row>
+    <row r="66" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K66" s="49"/>
+      <c r="L66" s="27"/>
+      <c r="M66" s="27"/>
+      <c r="N66" s="27"/>
+      <c r="O66" s="27"/>
+      <c r="P66" s="27"/>
+      <c r="Q66" s="27"/>
+      <c r="R66" s="27"/>
+      <c r="S66" s="27"/>
+      <c r="T66" s="27"/>
+      <c r="U66" s="27"/>
+    </row>
+    <row r="67" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K67" s="49"/>
+      <c r="L67" s="27"/>
+      <c r="M67" s="27"/>
+      <c r="N67" s="27"/>
+      <c r="O67" s="27"/>
+      <c r="P67" s="27"/>
+      <c r="Q67" s="27"/>
+      <c r="R67" s="27"/>
+      <c r="S67" s="27"/>
+      <c r="T67" s="27"/>
+      <c r="U67" s="27"/>
+    </row>
+    <row r="68" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K68" s="49"/>
+      <c r="L68" s="27"/>
+      <c r="M68" s="27"/>
+      <c r="N68" s="27"/>
+      <c r="O68" s="27"/>
+      <c r="P68" s="27"/>
+      <c r="Q68" s="27"/>
+      <c r="R68" s="27"/>
+      <c r="S68" s="27"/>
+      <c r="T68" s="27"/>
+      <c r="U68" s="27"/>
+    </row>
+    <row r="69" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K69" s="49"/>
+      <c r="L69" s="27"/>
+      <c r="M69" s="27"/>
+      <c r="N69" s="27"/>
+      <c r="O69" s="27"/>
+      <c r="P69" s="27"/>
+      <c r="Q69" s="27"/>
+      <c r="R69" s="27"/>
+      <c r="S69" s="27"/>
+      <c r="T69" s="27"/>
+      <c r="U69" s="27"/>
+    </row>
+    <row r="70" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K70" s="49"/>
+      <c r="L70" s="27"/>
+      <c r="M70" s="27"/>
+      <c r="N70" s="27"/>
+      <c r="O70" s="27"/>
+      <c r="P70" s="27"/>
+      <c r="Q70" s="27"/>
+      <c r="R70" s="27"/>
+      <c r="S70" s="27"/>
+      <c r="T70" s="27"/>
+      <c r="U70" s="27"/>
+    </row>
+    <row r="71" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K71" s="49"/>
+      <c r="L71" s="27"/>
+      <c r="M71" s="27"/>
+      <c r="N71" s="27"/>
+      <c r="O71" s="27"/>
+      <c r="P71" s="27"/>
+      <c r="Q71" s="27"/>
+      <c r="R71" s="27"/>
+      <c r="S71" s="27"/>
+      <c r="T71" s="27"/>
+      <c r="U71" s="27"/>
+    </row>
+    <row r="72" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K72" s="49"/>
+      <c r="L72" s="27"/>
+      <c r="M72" s="27"/>
+      <c r="N72" s="27"/>
+      <c r="O72" s="27"/>
+      <c r="P72" s="27"/>
+      <c r="Q72" s="27"/>
+      <c r="R72" s="27"/>
+      <c r="S72" s="27"/>
+      <c r="T72" s="27"/>
+      <c r="U72" s="27"/>
+    </row>
+    <row r="73" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K73" s="49"/>
+      <c r="L73" s="27"/>
+      <c r="M73" s="27"/>
+      <c r="N73" s="27"/>
+      <c r="O73" s="27"/>
+      <c r="P73" s="27"/>
+      <c r="Q73" s="27"/>
+      <c r="R73" s="27"/>
+      <c r="S73" s="27"/>
+      <c r="T73" s="27"/>
+      <c r="U73" s="27"/>
+    </row>
+    <row r="74" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K74" s="49"/>
+      <c r="L74" s="27"/>
+      <c r="M74" s="27"/>
+      <c r="N74" s="27"/>
+      <c r="O74" s="27"/>
+      <c r="P74" s="27"/>
+      <c r="Q74" s="27"/>
+      <c r="R74" s="27"/>
+      <c r="S74" s="27"/>
+      <c r="T74" s="27"/>
+      <c r="U74" s="27"/>
+    </row>
+    <row r="75" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K75" s="49"/>
+      <c r="L75" s="27"/>
+      <c r="M75" s="27"/>
+      <c r="N75" s="27"/>
+      <c r="O75" s="27"/>
+      <c r="P75" s="27"/>
+      <c r="Q75" s="27"/>
+      <c r="R75" s="27"/>
+      <c r="S75" s="27"/>
+      <c r="T75" s="27"/>
+      <c r="U75" s="27"/>
+    </row>
+    <row r="76" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K76" s="49"/>
+      <c r="L76" s="27"/>
+      <c r="M76" s="27"/>
+      <c r="N76" s="27"/>
+      <c r="O76" s="27"/>
+      <c r="P76" s="27"/>
+      <c r="Q76" s="27"/>
+      <c r="R76" s="27"/>
+      <c r="S76" s="27"/>
+      <c r="T76" s="27"/>
+      <c r="U76" s="27"/>
+    </row>
+    <row r="77" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K77" s="49"/>
+      <c r="L77" s="27"/>
+      <c r="M77" s="27"/>
+      <c r="N77" s="27"/>
+      <c r="O77" s="27"/>
+      <c r="P77" s="27"/>
+      <c r="Q77" s="27"/>
+      <c r="R77" s="27"/>
+      <c r="S77" s="27"/>
+      <c r="T77" s="27"/>
+      <c r="U77" s="27"/>
+    </row>
+    <row r="78" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K78" s="49"/>
+      <c r="L78" s="27"/>
+      <c r="M78" s="27"/>
+      <c r="N78" s="27"/>
+      <c r="O78" s="27"/>
+      <c r="P78" s="27"/>
+      <c r="Q78" s="27"/>
+      <c r="R78" s="27"/>
+      <c r="S78" s="27"/>
+      <c r="T78" s="27"/>
+      <c r="U78" s="27"/>
+    </row>
+    <row r="79" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K79" s="49"/>
+      <c r="L79" s="27"/>
+      <c r="M79" s="27"/>
+      <c r="N79" s="27"/>
+      <c r="O79" s="27"/>
+      <c r="P79" s="27"/>
+      <c r="Q79" s="27"/>
+      <c r="R79" s="27"/>
+      <c r="S79" s="27"/>
+      <c r="T79" s="27"/>
+      <c r="U79" s="27"/>
+    </row>
+    <row r="80" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K80" s="49"/>
+      <c r="L80" s="27"/>
+      <c r="M80" s="27"/>
+      <c r="N80" s="27"/>
+      <c r="O80" s="27"/>
+      <c r="P80" s="27"/>
+      <c r="Q80" s="27"/>
+      <c r="R80" s="27"/>
+      <c r="S80" s="27"/>
+      <c r="T80" s="27"/>
+      <c r="U80" s="27"/>
+    </row>
+    <row r="81" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K81" s="49"/>
+      <c r="L81" s="27"/>
+      <c r="M81" s="27"/>
+      <c r="N81" s="27"/>
+      <c r="O81" s="27"/>
+      <c r="P81" s="27"/>
+      <c r="Q81" s="27"/>
+      <c r="R81" s="27"/>
+      <c r="S81" s="27"/>
+      <c r="T81" s="27"/>
+      <c r="U81" s="27"/>
+    </row>
+    <row r="82" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K82" s="49"/>
+      <c r="L82" s="27"/>
+      <c r="M82" s="27"/>
+      <c r="N82" s="27"/>
+      <c r="O82" s="27"/>
+      <c r="P82" s="27"/>
+      <c r="Q82" s="27"/>
+      <c r="R82" s="27"/>
+      <c r="S82" s="27"/>
+      <c r="T82" s="27"/>
+      <c r="U82" s="27"/>
+    </row>
+    <row r="83" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K83" s="49"/>
+      <c r="L83" s="27"/>
+      <c r="M83" s="27"/>
+      <c r="N83" s="27"/>
+      <c r="O83" s="27"/>
+      <c r="P83" s="27"/>
+      <c r="Q83" s="27"/>
+      <c r="R83" s="27"/>
+      <c r="S83" s="27"/>
+      <c r="T83" s="27"/>
+      <c r="U83" s="27"/>
+    </row>
+    <row r="84" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K84" s="49"/>
+      <c r="L84" s="27"/>
+      <c r="M84" s="27"/>
+      <c r="N84" s="27"/>
+      <c r="O84" s="27"/>
+      <c r="P84" s="27"/>
+      <c r="Q84" s="27"/>
+      <c r="R84" s="27"/>
+      <c r="S84" s="27"/>
+      <c r="T84" s="27"/>
+      <c r="U84" s="27"/>
+    </row>
+    <row r="85" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K85" s="49"/>
+      <c r="L85" s="27"/>
+      <c r="M85" s="27"/>
+      <c r="N85" s="27"/>
+      <c r="O85" s="27"/>
+      <c r="P85" s="27"/>
+      <c r="Q85" s="27"/>
+      <c r="R85" s="27"/>
+      <c r="S85" s="27"/>
+      <c r="T85" s="27"/>
+      <c r="U85" s="27"/>
+    </row>
+    <row r="86" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K86" s="49"/>
+      <c r="L86" s="27"/>
+      <c r="M86" s="27"/>
+      <c r="N86" s="27"/>
+      <c r="O86" s="27"/>
+      <c r="P86" s="27"/>
+      <c r="Q86" s="27"/>
+      <c r="R86" s="27"/>
+      <c r="S86" s="27"/>
+      <c r="T86" s="27"/>
+      <c r="U86" s="27"/>
+    </row>
+    <row r="87" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K87" s="49"/>
+      <c r="L87" s="27"/>
+      <c r="M87" s="27"/>
+      <c r="N87" s="27"/>
+      <c r="O87" s="27"/>
+      <c r="P87" s="27"/>
+      <c r="Q87" s="27"/>
+      <c r="R87" s="27"/>
+      <c r="S87" s="27"/>
+      <c r="T87" s="27"/>
+      <c r="U87" s="27"/>
+    </row>
+    <row r="88" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K88" s="49"/>
+      <c r="L88" s="27"/>
+      <c r="M88" s="27"/>
+      <c r="N88" s="27"/>
+      <c r="O88" s="27"/>
+      <c r="P88" s="27"/>
+      <c r="Q88" s="27"/>
+      <c r="R88" s="27"/>
+      <c r="S88" s="27"/>
+      <c r="T88" s="27"/>
+      <c r="U88" s="27"/>
+    </row>
+    <row r="89" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K89" s="49"/>
+      <c r="L89" s="27"/>
+      <c r="M89" s="27"/>
+      <c r="N89" s="27"/>
+      <c r="O89" s="27"/>
+      <c r="P89" s="27"/>
+      <c r="Q89" s="27"/>
+      <c r="R89" s="27"/>
+      <c r="S89" s="27"/>
+      <c r="T89" s="27"/>
+      <c r="U89" s="27"/>
+    </row>
+    <row r="90" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K90" s="49"/>
+      <c r="L90" s="27"/>
+      <c r="M90" s="27"/>
+      <c r="N90" s="27"/>
+      <c r="O90" s="27"/>
+      <c r="P90" s="27"/>
+      <c r="Q90" s="27"/>
+      <c r="R90" s="27"/>
+      <c r="S90" s="27"/>
+      <c r="T90" s="27"/>
+      <c r="U90" s="27"/>
+    </row>
+    <row r="91" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K91" s="49"/>
+      <c r="L91" s="27"/>
+      <c r="M91" s="27"/>
+      <c r="N91" s="27"/>
+      <c r="O91" s="27"/>
+      <c r="P91" s="27"/>
+      <c r="Q91" s="27"/>
+      <c r="R91" s="27"/>
+      <c r="S91" s="27"/>
+      <c r="T91" s="27"/>
+      <c r="U91" s="27"/>
+    </row>
+    <row r="92" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K92" s="49"/>
+      <c r="L92" s="27"/>
+      <c r="M92" s="27"/>
+      <c r="N92" s="27"/>
+      <c r="O92" s="27"/>
+      <c r="P92" s="27"/>
+      <c r="Q92" s="27"/>
+      <c r="R92" s="27"/>
+      <c r="S92" s="27"/>
+      <c r="T92" s="27"/>
+      <c r="U92" s="27"/>
+    </row>
+    <row r="93" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K93" s="49"/>
+      <c r="L93" s="27"/>
+      <c r="M93" s="27"/>
+      <c r="N93" s="27"/>
+      <c r="O93" s="27"/>
+      <c r="P93" s="27"/>
+      <c r="Q93" s="27"/>
+      <c r="R93" s="27"/>
+      <c r="S93" s="27"/>
+      <c r="T93" s="27"/>
+      <c r="U93" s="27"/>
+    </row>
+    <row r="94" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K94" s="49"/>
+      <c r="L94" s="27"/>
+      <c r="M94" s="27"/>
+      <c r="N94" s="27"/>
+      <c r="O94" s="27"/>
+      <c r="P94" s="27"/>
+      <c r="Q94" s="27"/>
+      <c r="R94" s="27"/>
+      <c r="S94" s="27"/>
+      <c r="T94" s="27"/>
+      <c r="U94" s="27"/>
+    </row>
+    <row r="95" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K95" s="49"/>
+      <c r="L95" s="27"/>
+      <c r="M95" s="27"/>
+      <c r="N95" s="27"/>
+      <c r="O95" s="27"/>
+      <c r="P95" s="27"/>
+      <c r="Q95" s="27"/>
+      <c r="R95" s="27"/>
+      <c r="S95" s="27"/>
+      <c r="T95" s="27"/>
+      <c r="U95" s="27"/>
+    </row>
+    <row r="96" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K96" s="49"/>
+      <c r="L96" s="27"/>
+      <c r="M96" s="27"/>
+      <c r="N96" s="27"/>
+      <c r="O96" s="27"/>
+      <c r="P96" s="27"/>
+      <c r="Q96" s="27"/>
+      <c r="R96" s="27"/>
+      <c r="S96" s="27"/>
+      <c r="T96" s="27"/>
+      <c r="U96" s="27"/>
+    </row>
+    <row r="97" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K97" s="49"/>
+      <c r="L97" s="27"/>
+      <c r="M97" s="27"/>
+      <c r="N97" s="27"/>
+      <c r="O97" s="27"/>
+      <c r="P97" s="27"/>
+      <c r="Q97" s="27"/>
+      <c r="R97" s="27"/>
+      <c r="S97" s="27"/>
+      <c r="T97" s="27"/>
+      <c r="U97" s="27"/>
+    </row>
+    <row r="98" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K98" s="49"/>
+      <c r="L98" s="27"/>
+      <c r="M98" s="27"/>
+      <c r="N98" s="27"/>
+      <c r="O98" s="27"/>
+      <c r="P98" s="27"/>
+      <c r="Q98" s="27"/>
+      <c r="R98" s="27"/>
+      <c r="S98" s="27"/>
+      <c r="T98" s="27"/>
+      <c r="U98" s="27"/>
+    </row>
+    <row r="99" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K99" s="49"/>
+      <c r="L99" s="27"/>
+      <c r="M99" s="27"/>
+      <c r="N99" s="27"/>
+      <c r="O99" s="27"/>
+      <c r="P99" s="27"/>
+      <c r="Q99" s="27"/>
+      <c r="R99" s="27"/>
+      <c r="S99" s="27"/>
+      <c r="T99" s="27"/>
+      <c r="U99" s="27"/>
+    </row>
+    <row r="100" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K100" s="49"/>
+      <c r="L100" s="27"/>
+      <c r="M100" s="27"/>
+      <c r="N100" s="27"/>
+      <c r="O100" s="27"/>
+      <c r="P100" s="27"/>
+      <c r="Q100" s="27"/>
+      <c r="R100" s="27"/>
+      <c r="S100" s="27"/>
+      <c r="T100" s="27"/>
+      <c r="U100" s="27"/>
+    </row>
+    <row r="101" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K101" s="49"/>
+      <c r="L101" s="27"/>
+      <c r="M101" s="27"/>
+      <c r="N101" s="27"/>
+      <c r="O101" s="27"/>
+      <c r="P101" s="27"/>
+      <c r="Q101" s="27"/>
+      <c r="R101" s="27"/>
+      <c r="S101" s="27"/>
+      <c r="T101" s="27"/>
+      <c r="U101" s="27"/>
+    </row>
+    <row r="102" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K102" s="49"/>
+      <c r="L102" s="27"/>
+      <c r="M102" s="27"/>
+      <c r="N102" s="27"/>
+      <c r="O102" s="27"/>
+      <c r="P102" s="27"/>
+      <c r="Q102" s="27"/>
+      <c r="R102" s="27"/>
+      <c r="S102" s="27"/>
+      <c r="T102" s="27"/>
+      <c r="U102" s="27"/>
+    </row>
+    <row r="103" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K103" s="49"/>
+      <c r="L103" s="27"/>
+      <c r="M103" s="27"/>
+      <c r="N103" s="27"/>
+      <c r="O103" s="27"/>
+      <c r="P103" s="27"/>
+      <c r="Q103" s="27"/>
+      <c r="R103" s="27"/>
+      <c r="S103" s="27"/>
+      <c r="T103" s="27"/>
+      <c r="U103" s="27"/>
+    </row>
+    <row r="104" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K104" s="49"/>
+      <c r="L104" s="27"/>
+      <c r="M104" s="27"/>
+      <c r="N104" s="27"/>
+      <c r="O104" s="27"/>
+      <c r="P104" s="27"/>
+      <c r="Q104" s="27"/>
+      <c r="R104" s="27"/>
+      <c r="S104" s="27"/>
+      <c r="T104" s="27"/>
+      <c r="U104" s="27"/>
+    </row>
+    <row r="105" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K105" s="49"/>
+      <c r="L105" s="27"/>
+      <c r="M105" s="27"/>
+      <c r="N105" s="27"/>
+      <c r="O105" s="27"/>
+      <c r="P105" s="27"/>
+      <c r="Q105" s="27"/>
+      <c r="R105" s="27"/>
+      <c r="S105" s="27"/>
+      <c r="T105" s="27"/>
+      <c r="U105" s="27"/>
+    </row>
+    <row r="106" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K106" s="49"/>
+      <c r="L106" s="27"/>
+      <c r="M106" s="27"/>
+      <c r="N106" s="27"/>
+      <c r="O106" s="27"/>
+      <c r="P106" s="27"/>
+      <c r="Q106" s="27"/>
+      <c r="R106" s="27"/>
+      <c r="S106" s="27"/>
+      <c r="T106" s="27"/>
+      <c r="U106" s="27"/>
+    </row>
+    <row r="107" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K107" s="49"/>
+      <c r="L107" s="27"/>
+      <c r="M107" s="27"/>
+      <c r="N107" s="27"/>
+      <c r="O107" s="27"/>
+      <c r="P107" s="27"/>
+      <c r="Q107" s="27"/>
+      <c r="R107" s="27"/>
+      <c r="S107" s="27"/>
+      <c r="T107" s="27"/>
+      <c r="U107" s="27"/>
+    </row>
+    <row r="108" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K108" s="49"/>
+      <c r="L108" s="27"/>
+      <c r="M108" s="27"/>
+      <c r="N108" s="27"/>
+      <c r="O108" s="27"/>
+      <c r="P108" s="27"/>
+      <c r="Q108" s="27"/>
+      <c r="R108" s="27"/>
+      <c r="S108" s="27"/>
+      <c r="T108" s="27"/>
+      <c r="U108" s="27"/>
+    </row>
+    <row r="109" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K109" s="49"/>
+      <c r="L109" s="27"/>
+      <c r="M109" s="27"/>
+      <c r="N109" s="27"/>
+      <c r="O109" s="27"/>
+      <c r="P109" s="27"/>
+      <c r="Q109" s="27"/>
+      <c r="R109" s="27"/>
+      <c r="S109" s="27"/>
+      <c r="T109" s="27"/>
+      <c r="U109" s="27"/>
+    </row>
+    <row r="110" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K110" s="49"/>
+      <c r="L110" s="27"/>
+      <c r="M110" s="27"/>
+      <c r="N110" s="27"/>
+      <c r="O110" s="27"/>
+      <c r="P110" s="27"/>
+      <c r="Q110" s="27"/>
+      <c r="R110" s="27"/>
+      <c r="S110" s="27"/>
+      <c r="T110" s="27"/>
+      <c r="U110" s="27"/>
+    </row>
+    <row r="111" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K111" s="49"/>
+      <c r="L111" s="27"/>
+      <c r="M111" s="27"/>
+      <c r="N111" s="27"/>
+      <c r="O111" s="27"/>
+      <c r="P111" s="27"/>
+      <c r="Q111" s="27"/>
+      <c r="R111" s="27"/>
+      <c r="S111" s="27"/>
+      <c r="T111" s="27"/>
+      <c r="U111" s="27"/>
+    </row>
+    <row r="112" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K112" s="49"/>
+      <c r="L112" s="27"/>
+      <c r="M112" s="27"/>
+      <c r="N112" s="27"/>
+      <c r="O112" s="27"/>
+      <c r="P112" s="27"/>
+      <c r="Q112" s="27"/>
+      <c r="R112" s="27"/>
+      <c r="S112" s="27"/>
+      <c r="T112" s="27"/>
+      <c r="U112" s="27"/>
+    </row>
+    <row r="113" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K113" s="49"/>
+      <c r="L113" s="27"/>
+      <c r="M113" s="27"/>
+      <c r="N113" s="27"/>
+      <c r="O113" s="27"/>
+      <c r="P113" s="27"/>
+      <c r="Q113" s="27"/>
+      <c r="R113" s="27"/>
+      <c r="S113" s="27"/>
+      <c r="T113" s="27"/>
+      <c r="U113" s="27"/>
+    </row>
+    <row r="114" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K114" s="49"/>
+      <c r="L114" s="27"/>
+      <c r="M114" s="27"/>
+      <c r="N114" s="27"/>
+      <c r="O114" s="27"/>
+      <c r="P114" s="27"/>
+      <c r="Q114" s="27"/>
+      <c r="R114" s="27"/>
+      <c r="S114" s="27"/>
+      <c r="T114" s="27"/>
+      <c r="U114" s="27"/>
+    </row>
+    <row r="115" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K115" s="49"/>
+      <c r="L115" s="27"/>
+      <c r="M115" s="27"/>
+      <c r="N115" s="27"/>
+      <c r="O115" s="27"/>
+      <c r="P115" s="27"/>
+      <c r="Q115" s="27"/>
+      <c r="R115" s="27"/>
+      <c r="S115" s="27"/>
+      <c r="T115" s="27"/>
+      <c r="U115" s="27"/>
+    </row>
+    <row r="116" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K116" s="49"/>
+      <c r="L116" s="27"/>
+      <c r="M116" s="27"/>
+      <c r="N116" s="27"/>
+      <c r="O116" s="27"/>
+      <c r="P116" s="27"/>
+      <c r="Q116" s="27"/>
+      <c r="R116" s="27"/>
+      <c r="S116" s="27"/>
+      <c r="T116" s="27"/>
+      <c r="U116" s="27"/>
+    </row>
+    <row r="117" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K117" s="49"/>
+      <c r="L117" s="27"/>
+      <c r="M117" s="27"/>
+      <c r="N117" s="27"/>
+      <c r="O117" s="27"/>
+      <c r="P117" s="27"/>
+      <c r="Q117" s="27"/>
+      <c r="R117" s="27"/>
+      <c r="S117" s="27"/>
+      <c r="T117" s="27"/>
+      <c r="U117" s="27"/>
+    </row>
+    <row r="118" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K118" s="49"/>
+      <c r="L118" s="27"/>
+      <c r="M118" s="27"/>
+      <c r="N118" s="27"/>
+      <c r="O118" s="27"/>
+      <c r="P118" s="27"/>
+      <c r="Q118" s="27"/>
+      <c r="R118" s="27"/>
+      <c r="S118" s="27"/>
+      <c r="T118" s="27"/>
+      <c r="U118" s="27"/>
+    </row>
+    <row r="119" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K119" s="49"/>
+      <c r="L119" s="27"/>
+      <c r="M119" s="27"/>
+      <c r="N119" s="27"/>
+      <c r="O119" s="27"/>
+      <c r="P119" s="27"/>
+      <c r="Q119" s="27"/>
+      <c r="R119" s="27"/>
+      <c r="S119" s="27"/>
+      <c r="T119" s="27"/>
+      <c r="U119" s="27"/>
+    </row>
+    <row r="120" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K120" s="49"/>
+      <c r="L120" s="27"/>
+      <c r="M120" s="27"/>
+      <c r="N120" s="27"/>
+      <c r="O120" s="27"/>
+      <c r="P120" s="27"/>
+      <c r="Q120" s="27"/>
+      <c r="R120" s="27"/>
+      <c r="S120" s="27"/>
+      <c r="T120" s="27"/>
+      <c r="U120" s="27"/>
+    </row>
+    <row r="121" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K121" s="49"/>
+      <c r="L121" s="27"/>
+      <c r="M121" s="27"/>
+      <c r="N121" s="27"/>
+      <c r="O121" s="27"/>
+      <c r="P121" s="27"/>
+      <c r="Q121" s="27"/>
+      <c r="R121" s="27"/>
+      <c r="S121" s="27"/>
+      <c r="T121" s="27"/>
+      <c r="U121" s="27"/>
+    </row>
+    <row r="122" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K122" s="49"/>
+      <c r="L122" s="27"/>
+      <c r="M122" s="27"/>
+      <c r="N122" s="27"/>
+      <c r="O122" s="27"/>
+      <c r="P122" s="27"/>
+      <c r="Q122" s="27"/>
+      <c r="R122" s="27"/>
+      <c r="S122" s="27"/>
+      <c r="T122" s="27"/>
+      <c r="U122" s="27"/>
+    </row>
+    <row r="123" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K123" s="49"/>
+      <c r="L123" s="27"/>
+      <c r="M123" s="27"/>
+      <c r="N123" s="27"/>
+      <c r="O123" s="27"/>
+      <c r="P123" s="27"/>
+      <c r="Q123" s="27"/>
+      <c r="R123" s="27"/>
+      <c r="S123" s="27"/>
+      <c r="T123" s="27"/>
+      <c r="U123" s="27"/>
+    </row>
+    <row r="124" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K124" s="49"/>
+      <c r="L124" s="27"/>
+      <c r="M124" s="27"/>
+      <c r="N124" s="27"/>
+      <c r="O124" s="27"/>
+      <c r="P124" s="27"/>
+      <c r="Q124" s="27"/>
+      <c r="R124" s="27"/>
+      <c r="S124" s="27"/>
+      <c r="T124" s="27"/>
+      <c r="U124" s="27"/>
+    </row>
+    <row r="125" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K125" s="49"/>
+      <c r="L125" s="27"/>
+      <c r="M125" s="27"/>
+      <c r="N125" s="27"/>
+      <c r="O125" s="27"/>
+      <c r="P125" s="27"/>
+      <c r="Q125" s="27"/>
+      <c r="R125" s="27"/>
+      <c r="S125" s="27"/>
+      <c r="T125" s="27"/>
+      <c r="U125" s="27"/>
+    </row>
+    <row r="126" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K126" s="49"/>
+      <c r="L126" s="27"/>
+      <c r="M126" s="27"/>
+      <c r="N126" s="27"/>
+      <c r="O126" s="27"/>
+      <c r="P126" s="27"/>
+      <c r="Q126" s="27"/>
+      <c r="R126" s="27"/>
+      <c r="S126" s="27"/>
+      <c r="T126" s="27"/>
+      <c r="U126" s="27"/>
+    </row>
+    <row r="127" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K127" s="49"/>
+      <c r="L127" s="27"/>
+      <c r="M127" s="27"/>
+      <c r="N127" s="27"/>
+      <c r="O127" s="27"/>
+      <c r="P127" s="27"/>
+      <c r="Q127" s="27"/>
+      <c r="R127" s="27"/>
+      <c r="S127" s="27"/>
+      <c r="T127" s="27"/>
+      <c r="U127" s="27"/>
+    </row>
+    <row r="128" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K128" s="49"/>
+      <c r="L128" s="27"/>
+      <c r="M128" s="27"/>
+      <c r="N128" s="27"/>
+      <c r="O128" s="27"/>
+      <c r="P128" s="27"/>
+      <c r="Q128" s="27"/>
+      <c r="R128" s="27"/>
+      <c r="S128" s="27"/>
+      <c r="T128" s="27"/>
+      <c r="U128" s="27"/>
+    </row>
+    <row r="129" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K129" s="49"/>
+      <c r="L129" s="27"/>
+      <c r="M129" s="27"/>
+      <c r="N129" s="27"/>
+      <c r="O129" s="27"/>
+      <c r="P129" s="27"/>
+      <c r="Q129" s="27"/>
+      <c r="R129" s="27"/>
+      <c r="S129" s="27"/>
+      <c r="T129" s="27"/>
+      <c r="U129" s="27"/>
+    </row>
+    <row r="130" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K130" s="49"/>
+      <c r="L130" s="27"/>
+      <c r="M130" s="27"/>
+      <c r="N130" s="27"/>
+      <c r="O130" s="27"/>
+      <c r="P130" s="27"/>
+      <c r="Q130" s="27"/>
+      <c r="R130" s="27"/>
+      <c r="S130" s="27"/>
+      <c r="T130" s="27"/>
+      <c r="U130" s="27"/>
+    </row>
+    <row r="131" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K131" s="49"/>
+      <c r="L131" s="27"/>
+      <c r="M131" s="27"/>
+      <c r="N131" s="27"/>
+      <c r="O131" s="27"/>
+      <c r="P131" s="27"/>
+      <c r="Q131" s="27"/>
+      <c r="R131" s="27"/>
+      <c r="S131" s="27"/>
+      <c r="T131" s="27"/>
+      <c r="U131" s="27"/>
+    </row>
+    <row r="132" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K132" s="49"/>
+      <c r="L132" s="27"/>
+      <c r="M132" s="27"/>
+      <c r="N132" s="27"/>
+      <c r="O132" s="27"/>
+      <c r="P132" s="27"/>
+      <c r="Q132" s="27"/>
+      <c r="R132" s="27"/>
+      <c r="S132" s="27"/>
+      <c r="T132" s="27"/>
+      <c r="U132" s="27"/>
+    </row>
+    <row r="133" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K133" s="49"/>
+      <c r="L133" s="27"/>
+      <c r="M133" s="27"/>
+      <c r="N133" s="27"/>
+      <c r="O133" s="27"/>
+      <c r="P133" s="27"/>
+      <c r="Q133" s="27"/>
+      <c r="R133" s="27"/>
+      <c r="S133" s="27"/>
+      <c r="T133" s="27"/>
+      <c r="U133" s="27"/>
+    </row>
+    <row r="134" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K134" s="49"/>
+      <c r="L134" s="27"/>
+      <c r="M134" s="27"/>
+      <c r="N134" s="27"/>
+      <c r="O134" s="27"/>
+      <c r="P134" s="27"/>
+      <c r="Q134" s="27"/>
+      <c r="R134" s="27"/>
+      <c r="S134" s="27"/>
+      <c r="T134" s="27"/>
+      <c r="U134" s="27"/>
+    </row>
+    <row r="135" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K135" s="49"/>
+      <c r="L135" s="27"/>
+      <c r="M135" s="27"/>
+      <c r="N135" s="27"/>
+      <c r="O135" s="27"/>
+      <c r="P135" s="27"/>
+      <c r="Q135" s="27"/>
+      <c r="R135" s="27"/>
+      <c r="S135" s="27"/>
+      <c r="T135" s="27"/>
+      <c r="U135" s="27"/>
+    </row>
+    <row r="136" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K136" s="49"/>
+      <c r="L136" s="27"/>
+      <c r="M136" s="27"/>
+      <c r="N136" s="27"/>
+      <c r="O136" s="27"/>
+      <c r="P136" s="27"/>
+      <c r="Q136" s="27"/>
+      <c r="R136" s="27"/>
+      <c r="S136" s="27"/>
+      <c r="T136" s="27"/>
+      <c r="U136" s="27"/>
+    </row>
+    <row r="137" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K137" s="49"/>
+      <c r="L137" s="27"/>
+      <c r="M137" s="27"/>
+      <c r="N137" s="27"/>
+      <c r="O137" s="27"/>
+      <c r="P137" s="27"/>
+      <c r="Q137" s="27"/>
+      <c r="R137" s="27"/>
+      <c r="S137" s="27"/>
+      <c r="T137" s="27"/>
+      <c r="U137" s="27"/>
+    </row>
+    <row r="138" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K138" s="49"/>
+      <c r="L138" s="27"/>
+      <c r="M138" s="27"/>
+      <c r="N138" s="27"/>
+      <c r="O138" s="27"/>
+      <c r="P138" s="27"/>
+      <c r="Q138" s="27"/>
+      <c r="R138" s="27"/>
+      <c r="S138" s="27"/>
+      <c r="T138" s="27"/>
+      <c r="U138" s="27"/>
+    </row>
+    <row r="139" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K139" s="49"/>
+      <c r="L139" s="27"/>
+      <c r="M139" s="27"/>
+      <c r="N139" s="27"/>
+      <c r="O139" s="27"/>
+      <c r="P139" s="27"/>
+      <c r="Q139" s="27"/>
+      <c r="R139" s="27"/>
+      <c r="S139" s="27"/>
+      <c r="T139" s="27"/>
+      <c r="U139" s="27"/>
+    </row>
+    <row r="140" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K140" s="49"/>
+      <c r="L140" s="27"/>
+      <c r="M140" s="27"/>
+      <c r="N140" s="27"/>
+      <c r="O140" s="27"/>
+      <c r="P140" s="27"/>
+      <c r="Q140" s="27"/>
+      <c r="R140" s="27"/>
+      <c r="S140" s="27"/>
+      <c r="T140" s="27"/>
+      <c r="U140" s="27"/>
+    </row>
+    <row r="141" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K141" s="49"/>
+      <c r="L141" s="27"/>
+      <c r="M141" s="27"/>
+      <c r="N141" s="27"/>
+      <c r="O141" s="27"/>
+      <c r="P141" s="27"/>
+      <c r="Q141" s="27"/>
+      <c r="R141" s="27"/>
+      <c r="S141" s="27"/>
+      <c r="T141" s="27"/>
+      <c r="U141" s="27"/>
+    </row>
+    <row r="142" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K142" s="49"/>
+      <c r="L142" s="27"/>
+      <c r="M142" s="27"/>
+      <c r="N142" s="27"/>
+      <c r="O142" s="27"/>
+      <c r="P142" s="27"/>
+      <c r="Q142" s="27"/>
+      <c r="R142" s="27"/>
+      <c r="S142" s="27"/>
+      <c r="T142" s="27"/>
+      <c r="U142" s="27"/>
+    </row>
+    <row r="143" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K143" s="49"/>
+      <c r="L143" s="27"/>
+      <c r="M143" s="27"/>
+      <c r="N143" s="27"/>
+      <c r="O143" s="27"/>
+      <c r="P143" s="27"/>
+      <c r="Q143" s="27"/>
+      <c r="R143" s="27"/>
+      <c r="S143" s="27"/>
+      <c r="T143" s="27"/>
+      <c r="U143" s="27"/>
+    </row>
+    <row r="144" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K144" s="49"/>
+      <c r="L144" s="27"/>
+      <c r="M144" s="27"/>
+      <c r="N144" s="27"/>
+      <c r="O144" s="27"/>
+      <c r="P144" s="27"/>
+      <c r="Q144" s="27"/>
+      <c r="R144" s="27"/>
+      <c r="S144" s="27"/>
+      <c r="T144" s="27"/>
+      <c r="U144" s="27"/>
+    </row>
+    <row r="145" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K145" s="49"/>
+      <c r="L145" s="27"/>
+      <c r="M145" s="27"/>
+      <c r="N145" s="27"/>
+      <c r="O145" s="27"/>
+      <c r="P145" s="27"/>
+      <c r="Q145" s="27"/>
+      <c r="R145" s="27"/>
+      <c r="S145" s="27"/>
+      <c r="T145" s="27"/>
+      <c r="U145" s="27"/>
+    </row>
+    <row r="146" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K146" s="49"/>
+      <c r="L146" s="27"/>
+      <c r="M146" s="27"/>
+      <c r="N146" s="27"/>
+      <c r="O146" s="27"/>
+      <c r="P146" s="27"/>
+      <c r="Q146" s="27"/>
+      <c r="R146" s="27"/>
+      <c r="S146" s="27"/>
+      <c r="T146" s="27"/>
+      <c r="U146" s="27"/>
+    </row>
+    <row r="147" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K147" s="49"/>
+      <c r="L147" s="27"/>
+      <c r="M147" s="27"/>
+      <c r="N147" s="27"/>
+      <c r="O147" s="27"/>
+      <c r="P147" s="27"/>
+      <c r="Q147" s="27"/>
+      <c r="R147" s="27"/>
+      <c r="S147" s="27"/>
+      <c r="T147" s="27"/>
+      <c r="U147" s="27"/>
+    </row>
+    <row r="148" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K148" s="49"/>
+      <c r="L148" s="27"/>
+      <c r="M148" s="27"/>
+      <c r="N148" s="27"/>
+      <c r="O148" s="27"/>
+      <c r="P148" s="27"/>
+      <c r="Q148" s="27"/>
+      <c r="R148" s="27"/>
+      <c r="S148" s="27"/>
+      <c r="T148" s="27"/>
+      <c r="U148" s="27"/>
+    </row>
+    <row r="149" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K149" s="49"/>
+      <c r="L149" s="27"/>
+      <c r="M149" s="27"/>
+      <c r="N149" s="27"/>
+      <c r="O149" s="27"/>
+      <c r="P149" s="27"/>
+      <c r="Q149" s="27"/>
+      <c r="R149" s="27"/>
+      <c r="S149" s="27"/>
+      <c r="T149" s="27"/>
+      <c r="U149" s="27"/>
+    </row>
+    <row r="150" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K150" s="49"/>
+      <c r="L150" s="27"/>
+      <c r="M150" s="27"/>
+      <c r="N150" s="27"/>
+      <c r="O150" s="27"/>
+      <c r="P150" s="27"/>
+      <c r="Q150" s="27"/>
+      <c r="R150" s="27"/>
+      <c r="S150" s="27"/>
+      <c r="T150" s="27"/>
+      <c r="U150" s="27"/>
+    </row>
+    <row r="151" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K151" s="49"/>
+      <c r="L151" s="27"/>
+      <c r="M151" s="27"/>
+      <c r="N151" s="27"/>
+      <c r="O151" s="27"/>
+      <c r="P151" s="27"/>
+      <c r="Q151" s="27"/>
+      <c r="R151" s="27"/>
+      <c r="S151" s="27"/>
+      <c r="T151" s="27"/>
+      <c r="U151" s="27"/>
+    </row>
+    <row r="152" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K152" s="49"/>
+      <c r="L152" s="27"/>
+      <c r="M152" s="27"/>
+      <c r="N152" s="27"/>
+      <c r="O152" s="27"/>
+      <c r="P152" s="27"/>
+      <c r="Q152" s="27"/>
+      <c r="R152" s="27"/>
+      <c r="S152" s="27"/>
+      <c r="T152" s="27"/>
+      <c r="U152" s="27"/>
+    </row>
+    <row r="153" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K153" s="49"/>
+      <c r="L153" s="27"/>
+      <c r="M153" s="27"/>
+      <c r="N153" s="27"/>
+      <c r="O153" s="27"/>
+      <c r="P153" s="27"/>
+      <c r="Q153" s="27"/>
+      <c r="R153" s="27"/>
+      <c r="S153" s="27"/>
+      <c r="T153" s="27"/>
+      <c r="U153" s="27"/>
+    </row>
+    <row r="154" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K154" s="49"/>
+      <c r="L154" s="27"/>
+      <c r="M154" s="27"/>
+      <c r="N154" s="27"/>
+      <c r="O154" s="27"/>
+      <c r="P154" s="27"/>
+      <c r="Q154" s="27"/>
+      <c r="R154" s="27"/>
+      <c r="S154" s="27"/>
+      <c r="T154" s="27"/>
+      <c r="U154" s="27"/>
+    </row>
+    <row r="155" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K155" s="49"/>
+      <c r="L155" s="27"/>
+      <c r="M155" s="27"/>
+      <c r="N155" s="27"/>
+      <c r="O155" s="27"/>
+      <c r="P155" s="27"/>
+      <c r="Q155" s="27"/>
+      <c r="R155" s="27"/>
+      <c r="S155" s="27"/>
+      <c r="T155" s="27"/>
+      <c r="U155" s="27"/>
+    </row>
+    <row r="156" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K156" s="49"/>
+      <c r="L156" s="27"/>
+      <c r="M156" s="27"/>
+      <c r="N156" s="27"/>
+      <c r="O156" s="27"/>
+      <c r="P156" s="27"/>
+      <c r="Q156" s="27"/>
+      <c r="R156" s="27"/>
+      <c r="S156" s="27"/>
+      <c r="T156" s="27"/>
+      <c r="U156" s="27"/>
+    </row>
+    <row r="157" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K157" s="49"/>
+      <c r="L157" s="27"/>
+      <c r="M157" s="27"/>
+      <c r="N157" s="27"/>
+      <c r="O157" s="27"/>
+      <c r="P157" s="27"/>
+      <c r="Q157" s="27"/>
+      <c r="R157" s="27"/>
+      <c r="S157" s="27"/>
+      <c r="T157" s="27"/>
+      <c r="U157" s="27"/>
+    </row>
+    <row r="158" spans="11:21" x14ac:dyDescent="0.25">
+      <c r="K158" s="49"/>
+      <c r="L158" s="27"/>
+      <c r="M158" s="27"/>
+      <c r="N158" s="27"/>
+      <c r="O158" s="27"/>
+      <c r="P158" s="27"/>
+      <c r="Q158" s="27"/>
+      <c r="R158" s="27"/>
+      <c r="S158" s="27"/>
+      <c r="T158" s="27"/>
+      <c r="U158" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="N21:S21"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="N19:S19"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1540268B-B206-4F4D-8979-E712B9521EA3}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:AA159"/>
